--- a/docs/data/jp/xlsx/372A.xlsx
+++ b/docs/data/jp/xlsx/372A.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC185"/>
+  <dimension ref="A1:AC192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4061,11 +4064,11 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.23)</t>
+          <t>현재 주가 (2026.10.26)</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>6100</v>
+        <v>6330</v>
       </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
@@ -5302,7 +5305,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.23</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5530,3532 +5533,3868 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>8479.502</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>8633.911</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>8333.184999999999</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>8754.097</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>8809.763999999999</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>9262.244000000001</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>9006.092000000001</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>8633.911</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>9262.244000000001</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>4272.17</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>3142.073</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>4334.593</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>4872.89</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>4816.553</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>3761.974</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>5090.802</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>3142.073</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>3761.974</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 전입</t>
-        </is>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>28.414</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>12.387</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>44.623</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>103.242</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>12.934</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>6.817</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>31.893</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>12.387</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>6.817</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>급여·수당</t>
-        </is>
-      </c>
-      <c r="H82" s="22" t="n">
-        <v>960.693</v>
-      </c>
-      <c r="I82" s="22" t="n">
-        <v>1010.099</v>
-      </c>
-      <c r="J82" s="22" t="n">
-        <v>1055.721</v>
-      </c>
-      <c r="K82" s="22" t="n">
-        <v>1072.158</v>
-      </c>
-      <c r="L82" s="22" t="n">
-        <v>1107.592</v>
-      </c>
-      <c r="M82" s="22" t="n">
-        <v>1209.891</v>
-      </c>
-      <c r="N82" s="22" t="n">
-        <v>1189.493</v>
-      </c>
-      <c r="W82" s="22" t="n">
-        <v>1010.099</v>
-      </c>
-      <c r="X82" s="22" t="n">
-        <v>1209.891</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>상여충당금 전입</t>
+          <t>대손충당금 전입</t>
         </is>
       </c>
       <c r="H83" s="22" t="n">
-        <v>-98.133</v>
+        <v>28.414</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>397.305</v>
+        <v>12.387</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>358.005</v>
+        <v>44.623</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>280.315</v>
+        <v>103.242</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>-111.707</v>
+        <v>12.934</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>385.563</v>
+        <v>6.817</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>402.931</v>
+        <v>31.893</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>397.305</v>
+        <v>12.387</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>385.563</v>
+        <v>6.817</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여비용</t>
+          <t>급여·수당</t>
         </is>
       </c>
       <c r="H84" s="22" t="n">
-        <v>51.803</v>
+        <v>960.693</v>
       </c>
       <c r="I84" s="22" t="n">
-        <v>63.362</v>
+        <v>1010.099</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>53.492</v>
+        <v>1055.721</v>
       </c>
       <c r="K84" s="22" t="n">
-        <v>53.471</v>
+        <v>1072.158</v>
       </c>
       <c r="L84" s="22" t="n">
-        <v>51.799</v>
+        <v>1107.592</v>
       </c>
       <c r="M84" s="22" t="n">
-        <v>60</v>
+        <v>1209.891</v>
       </c>
       <c r="N84" s="22" t="n">
-        <v>51.628</v>
+        <v>1189.493</v>
       </c>
       <c r="W84" s="22" t="n">
-        <v>63.362</v>
+        <v>1010.099</v>
       </c>
       <c r="X84" s="22" t="n">
-        <v>60</v>
+        <v>1209.891</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>지대·임차료</t>
+          <t>상여충당금 전입</t>
         </is>
       </c>
       <c r="H85" s="22" t="n">
-        <v>436.763</v>
+        <v>-98.133</v>
       </c>
       <c r="I85" s="22" t="n">
-        <v>406.465</v>
+        <v>397.305</v>
       </c>
       <c r="J85" s="22" t="n">
-        <v>447.154</v>
+        <v>358.005</v>
       </c>
       <c r="K85" s="22" t="n">
-        <v>454.656</v>
+        <v>280.315</v>
       </c>
       <c r="L85" s="22" t="n">
-        <v>483.267</v>
+        <v>-111.707</v>
       </c>
       <c r="M85" s="22" t="n">
-        <v>488.962</v>
+        <v>385.563</v>
       </c>
       <c r="N85" s="22" t="n">
-        <v>494.032</v>
+        <v>402.931</v>
       </c>
       <c r="W85" s="22" t="n">
-        <v>406.465</v>
+        <v>397.305</v>
       </c>
       <c r="X85" s="22" t="n">
-        <v>488.962</v>
+        <v>385.563</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>퇴직급여비용</t>
         </is>
       </c>
       <c r="H86" s="22" t="n">
-        <v>1509.074</v>
+        <v>51.803</v>
       </c>
       <c r="I86" s="22" t="n">
-        <v>1303.688</v>
+        <v>63.362</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>1249.141</v>
+        <v>53.492</v>
       </c>
       <c r="K86" s="22" t="n">
-        <v>1251.775</v>
+        <v>53.471</v>
       </c>
       <c r="L86" s="22" t="n">
-        <v>1765.414</v>
+        <v>51.799</v>
       </c>
       <c r="M86" s="22" t="n">
-        <v>1518.894</v>
+        <v>60</v>
       </c>
       <c r="N86" s="22" t="n">
-        <v>1382.638</v>
+        <v>51.628</v>
       </c>
       <c r="W86" s="22" t="n">
-        <v>1303.688</v>
+        <v>63.362</v>
       </c>
       <c r="X86" s="22" t="n">
-        <v>1518.894</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>판매비와 관리비 합계</t>
+          <t>지대·임차료</t>
         </is>
       </c>
       <c r="H87" s="22" t="n">
-        <v>2888.613</v>
+        <v>436.763</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>3193.307</v>
+        <v>406.465</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>3208.138</v>
+        <v>447.154</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>3215.619</v>
+        <v>454.656</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>3309.297</v>
+        <v>483.267</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>3670.127</v>
+        <v>488.962</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>3552.617</v>
+        <v>494.032</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>3193.307</v>
+        <v>406.465</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>3670.127</v>
+        <v>488.962</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>1383.556</v>
-      </c>
-      <c r="I88" s="12" t="n">
-        <v>-51.233</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>1126.454</v>
-      </c>
-      <c r="K88" s="12" t="n">
-        <v>1657.271</v>
-      </c>
-      <c r="L88" s="12" t="n">
-        <v>1507.257</v>
-      </c>
-      <c r="M88" s="12" t="n">
-        <v>91.84699999999999</v>
-      </c>
-      <c r="N88" s="12" t="n">
-        <v>1538.184</v>
-      </c>
-      <c r="W88" s="12" t="n">
-        <v>-51.233</v>
-      </c>
-      <c r="X88" s="12" t="n">
-        <v>91.84699999999999</v>
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="H88" s="22" t="n">
+        <v>1509.074</v>
+      </c>
+      <c r="I88" s="22" t="n">
+        <v>1303.688</v>
+      </c>
+      <c r="J88" s="22" t="n">
+        <v>1249.141</v>
+      </c>
+      <c r="K88" s="22" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="L88" s="22" t="n">
+        <v>1765.414</v>
+      </c>
+      <c r="M88" s="22" t="n">
+        <v>1518.894</v>
+      </c>
+      <c r="N88" s="22" t="n">
+        <v>1382.638</v>
+      </c>
+      <c r="W88" s="22" t="n">
+        <v>1303.688</v>
+      </c>
+      <c r="X88" s="22" t="n">
+        <v>1518.894</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비 합계</t>
         </is>
       </c>
       <c r="H89" s="22" t="n">
-        <v>3.766</v>
+        <v>2888.613</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>2.686</v>
+        <v>3193.307</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>6.725</v>
+        <v>3208.138</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>2.107</v>
+        <v>3215.619</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>9.109999999999999</v>
+        <v>3309.297</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>5.203</v>
+        <v>3670.127</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>13.282</v>
+        <v>3552.617</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>2.686</v>
+        <v>3193.307</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>5.203</v>
+        <v>3670.127</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="H90" s="22" t="n">
-        <v>3.515</v>
-      </c>
-      <c r="I90" s="22" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="J90" s="22" t="n">
-        <v>6.274</v>
-      </c>
-      <c r="K90" s="22" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="L90" s="22" t="n">
-        <v>3.781</v>
-      </c>
-      <c r="M90" s="22" t="n">
-        <v>1.323</v>
-      </c>
-      <c r="N90" s="22" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="W90" s="22" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="X90" s="22" t="n">
-        <v>1.323</v>
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>1383.556</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>-51.233</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>1126.454</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>1657.271</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>1507.257</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>91.84699999999999</v>
+      </c>
+      <c r="N90" s="12" t="n">
+        <v>1538.184</v>
+      </c>
+      <c r="W90" s="12" t="n">
+        <v>-51.233</v>
+      </c>
+      <c r="X90" s="12" t="n">
+        <v>91.84699999999999</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="20" t="inlineStr">
-        <is>
-          <t>보험금 수익</t>
-        </is>
-      </c>
-      <c r="H91" s="22" t="n">
-        <v>2.797</v>
-      </c>
-      <c r="I91" s="22" t="n">
-        <v>7.317</v>
-      </c>
-      <c r="J91" s="22" t="n">
-        <v>2.926</v>
-      </c>
-      <c r="K91" s="22" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>3.339</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>4.825</v>
-      </c>
-      <c r="N91" s="22" t="n">
-        <v>5.775</v>
-      </c>
-      <c r="W91" s="22" t="n">
-        <v>7.317</v>
-      </c>
-      <c r="X91" s="22" t="n">
-        <v>4.825</v>
+      <c r="A91" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="H91" s="17">
+        <f>IF(OR(H90="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H90/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I91" s="17">
+        <f>IF(OR(I90="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I90/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J91" s="17">
+        <f>IF(OR(J90="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J90/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K91" s="17">
+        <f>IF(OR(K90="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K90/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L91" s="17">
+        <f>IF(OR(L90="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L90/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M91" s="17">
+        <f>IF(OR(M90="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M90/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N91" s="17">
+        <f>IF(OR(N90="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N90/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="W91" s="17">
+        <f>IF(OR(W90="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W90/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X91" s="17">
+        <f>IF(OR(X90="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X90/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="20" t="inlineStr">
-        <is>
-          <t>임대료 수익</t>
-        </is>
-      </c>
-      <c r="H92" s="22" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="I92" s="22" t="n">
-        <v>7.113</v>
-      </c>
-      <c r="J92" s="22" t="n">
-        <v>7.107</v>
-      </c>
-      <c r="K92" s="22" t="n">
-        <v>7.109</v>
-      </c>
-      <c r="L92" s="22" t="n">
-        <v>13.894</v>
-      </c>
-      <c r="M92" s="22" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="N92" s="22" t="n">
-        <v>11.819</v>
-      </c>
-      <c r="W92" s="22" t="n">
-        <v>7.113</v>
-      </c>
-      <c r="X92" s="22" t="n">
-        <v>0.308</v>
+      <c r="A92" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="H92" s="17">
+        <f>IF(OR(H90="",D90=""),"",IF(D90&lt;=0,"",IFERROR(H90/D90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I92" s="17">
+        <f>IF(OR(I90="",E90=""),"",IF(E90&lt;=0,"",IFERROR(I90/E90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J92" s="17">
+        <f>IF(OR(J90="",F90=""),"",IF(F90&lt;=0,"",IFERROR(J90/F90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K92" s="17">
+        <f>IF(OR(K90="",G90=""),"",IF(G90&lt;=0,"",IFERROR(K90/G90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L92" s="17">
+        <f>IF(OR(L90="",H90=""),"",IF(H90&lt;=0,"",IFERROR(L90/H90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M92" s="17">
+        <f>IF(OR(M90="",I90=""),"",IF(I90&lt;=0,"",IFERROR(M90/I90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N92" s="17">
+        <f>IF(OR(N90="",J90=""),"",IF(J90&lt;=0,"",IFERROR(N90/J90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W92" s="17">
+        <f>IF(OR(W90="",V90=""),"",IF(V90&lt;=0,"",IFERROR(W90/V90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X92" s="17">
+        <f>IF(OR(X90="",W90=""),"",IF(W90&lt;=0,"",IFERROR(X90/W90-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>외환차익</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="H93" s="22" t="n">
-        <v>1.142</v>
+        <v>3.766</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>4.477</v>
+        <v>2.686</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>26.842</v>
+        <v>6.725</v>
       </c>
       <c r="K93" s="22" t="n">
-        <v>62.514</v>
+        <v>2.107</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>33.02</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>-23.474</v>
+        <v>5.203</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>0</v>
+        <v>13.282</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>4.477</v>
+        <v>2.686</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>-23.474</v>
+        <v>5.203</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>작업부산물 매각이익</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="H94" s="22" t="n">
-        <v>9.689</v>
+        <v>3.515</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>8.731999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>8.211</v>
+        <v>6.274</v>
       </c>
       <c r="K94" s="22" t="n">
-        <v>8.356</v>
+        <v>0.315</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>11.394</v>
+        <v>3.781</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>22.894</v>
+        <v>1.323</v>
       </c>
       <c r="N94" s="22" t="n">
-        <v>11.316</v>
+        <v>7.56</v>
       </c>
       <c r="W94" s="22" t="n">
-        <v>8.731999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="X94" s="22" t="n">
-        <v>22.894</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보험금 수익</t>
         </is>
       </c>
       <c r="H95" s="22" t="n">
-        <v>11.928</v>
+        <v>2.797</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>-14.597</v>
+        <v>7.317</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>17.511</v>
+        <v>2.926</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>15.39</v>
+        <v>2.271</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>15.429</v>
+        <v>3.339</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>22.498</v>
+        <v>4.825</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>23.036</v>
+        <v>5.775</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>-14.597</v>
+        <v>7.317</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>22.498</v>
+        <v>4.825</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>임대료 수익</t>
         </is>
       </c>
       <c r="H96" s="22" t="n">
-        <v>39.947</v>
+        <v>7.11</v>
       </c>
       <c r="I96" s="22" t="n">
-        <v>42.455</v>
+        <v>7.113</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>75.59999999999999</v>
+        <v>7.107</v>
       </c>
       <c r="K96" s="22" t="n">
-        <v>98.063</v>
+        <v>7.109</v>
       </c>
       <c r="L96" s="22" t="n">
-        <v>89.965</v>
+        <v>13.894</v>
       </c>
       <c r="M96" s="22" t="n">
-        <v>42.806</v>
+        <v>0.308</v>
       </c>
       <c r="N96" s="22" t="n">
-        <v>72.79000000000001</v>
+        <v>11.819</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>42.455</v>
+        <v>7.113</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>42.806</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="H97" s="22" t="n">
-        <v>119.472</v>
+        <v>1.142</v>
       </c>
       <c r="I97" s="22" t="n">
-        <v>141.278</v>
+        <v>4.477</v>
       </c>
       <c r="J97" s="22" t="n">
-        <v>137.795</v>
+        <v>26.842</v>
       </c>
       <c r="K97" s="22" t="n">
-        <v>148.641</v>
+        <v>62.514</v>
       </c>
       <c r="L97" s="22" t="n">
-        <v>165.168</v>
+        <v>33.02</v>
       </c>
       <c r="M97" s="22" t="n">
-        <v>187.722</v>
+        <v>-23.474</v>
       </c>
       <c r="N97" s="22" t="n">
-        <v>204.814</v>
+        <v>0</v>
       </c>
       <c r="W97" s="22" t="n">
-        <v>141.278</v>
+        <v>4.477</v>
       </c>
       <c r="X97" s="22" t="n">
-        <v>187.722</v>
+        <v>-23.474</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>작업부산물 매각이익</t>
         </is>
       </c>
       <c r="H98" s="22" t="n">
-        <v>1.831</v>
+        <v>9.689</v>
       </c>
       <c r="I98" s="22" t="n">
-        <v>58.39</v>
+        <v>8.731999999999999</v>
       </c>
       <c r="J98" s="22" t="n">
-        <v>7.23</v>
+        <v>8.211</v>
       </c>
       <c r="K98" s="22" t="n">
-        <v>2.971</v>
+        <v>8.356</v>
       </c>
       <c r="L98" s="22" t="n">
-        <v>3.136</v>
+        <v>11.394</v>
       </c>
       <c r="M98" s="22" t="n">
-        <v>66.90600000000001</v>
+        <v>22.894</v>
       </c>
       <c r="N98" s="22" t="n">
-        <v>4.285</v>
+        <v>11.316</v>
       </c>
       <c r="W98" s="22" t="n">
-        <v>58.39</v>
+        <v>8.731999999999999</v>
       </c>
       <c r="X98" s="22" t="n">
-        <v>66.90600000000001</v>
+        <v>22.894</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>지분법손실</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="H99" s="22" t="n">
-        <v>5.41</v>
+        <v>11.928</v>
       </c>
       <c r="I99" s="22" t="n">
-        <v>-6.479</v>
+        <v>-14.597</v>
       </c>
       <c r="J99" s="22" t="n">
-        <v>67.94</v>
+        <v>17.511</v>
       </c>
       <c r="K99" s="22" t="n">
-        <v>-23.899</v>
+        <v>15.39</v>
       </c>
       <c r="L99" s="22" t="n">
-        <v>-14.157</v>
+        <v>15.429</v>
       </c>
       <c r="M99" s="22" t="n">
-        <v>-18.751</v>
+        <v>22.498</v>
       </c>
       <c r="N99" s="22" t="n">
-        <v>28.949</v>
+        <v>23.036</v>
       </c>
       <c r="W99" s="22" t="n">
-        <v>-6.479</v>
+        <v>-14.597</v>
       </c>
       <c r="X99" s="22" t="n">
-        <v>-18.751</v>
+        <v>22.498</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="H100" s="22" t="n">
+        <v>39.947</v>
+      </c>
+      <c r="I100" s="22" t="n">
+        <v>42.455</v>
       </c>
       <c r="J100" s="22" t="n">
-        <v>0</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="K100" s="22" t="n">
+        <v>98.063</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <v>89.965</v>
+      </c>
+      <c r="M100" s="22" t="n">
+        <v>42.806</v>
       </c>
       <c r="N100" s="22" t="n">
-        <v>15.231</v>
+        <v>72.79000000000001</v>
+      </c>
+      <c r="W100" s="22" t="n">
+        <v>42.455</v>
+      </c>
+      <c r="X100" s="22" t="n">
+        <v>42.806</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="H101" s="22" t="n">
-        <v>2.831</v>
+        <v>119.472</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>39.175</v>
+        <v>141.278</v>
       </c>
       <c r="J101" s="22" t="n">
-        <v>2.735</v>
+        <v>137.795</v>
       </c>
       <c r="K101" s="22" t="n">
-        <v>3.28</v>
+        <v>148.641</v>
       </c>
       <c r="L101" s="22" t="n">
-        <v>3.107</v>
+        <v>165.168</v>
       </c>
       <c r="M101" s="22" t="n">
-        <v>2.802</v>
+        <v>187.722</v>
       </c>
       <c r="N101" s="22" t="n">
-        <v>3.991</v>
+        <v>204.814</v>
       </c>
       <c r="W101" s="22" t="n">
-        <v>39.175</v>
+        <v>141.278</v>
       </c>
       <c r="X101" s="22" t="n">
-        <v>2.802</v>
+        <v>187.722</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>지급수수료</t>
         </is>
       </c>
       <c r="H102" s="22" t="n">
-        <v>129.545</v>
+        <v>1.831</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>232.364</v>
+        <v>58.39</v>
       </c>
       <c r="J102" s="22" t="n">
-        <v>215.703</v>
+        <v>7.23</v>
       </c>
       <c r="K102" s="22" t="n">
-        <v>130.992</v>
+        <v>2.971</v>
       </c>
       <c r="L102" s="22" t="n">
-        <v>157.253</v>
+        <v>3.136</v>
       </c>
       <c r="M102" s="22" t="n">
-        <v>238.679</v>
+        <v>66.90600000000001</v>
       </c>
       <c r="N102" s="22" t="n">
-        <v>257.272</v>
+        <v>4.285</v>
       </c>
       <c r="W102" s="22" t="n">
-        <v>232.364</v>
+        <v>58.39</v>
       </c>
       <c r="X102" s="22" t="n">
-        <v>238.679</v>
+        <v>66.90600000000001</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>1293.958</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>-241.142</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>986.351</v>
-      </c>
-      <c r="K103" s="12" t="n">
-        <v>1624.342</v>
-      </c>
-      <c r="L103" s="12" t="n">
-        <v>1439.969</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>-104.026</v>
-      </c>
-      <c r="N103" s="12" t="n">
-        <v>1353.702</v>
-      </c>
-      <c r="W103" s="12" t="n">
-        <v>-241.142</v>
-      </c>
-      <c r="X103" s="12" t="n">
-        <v>-104.026</v>
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t>지분법손실</t>
+        </is>
+      </c>
+      <c r="H103" s="22" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="I103" s="22" t="n">
+        <v>-6.479</v>
+      </c>
+      <c r="J103" s="22" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="K103" s="22" t="n">
+        <v>-23.899</v>
+      </c>
+      <c r="L103" s="22" t="n">
+        <v>-14.157</v>
+      </c>
+      <c r="M103" s="22" t="n">
+        <v>-18.751</v>
+      </c>
+      <c r="N103" s="22" t="n">
+        <v>28.949</v>
+      </c>
+      <c r="W103" s="22" t="n">
+        <v>-6.479</v>
+      </c>
+      <c r="X103" s="22" t="n">
+        <v>-18.751</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각이익</t>
-        </is>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>8.991</v>
-      </c>
-      <c r="I104" s="22" t="n">
-        <v>3.527</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="J104" s="22" t="n">
-        <v>3.061</v>
-      </c>
-      <c r="K104" s="22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="L104" s="22" t="n">
-        <v>2.408</v>
-      </c>
-      <c r="M104" s="22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N104" s="22" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="W104" s="22" t="n">
-        <v>3.527</v>
-      </c>
-      <c r="X104" s="22" t="n">
-        <v>1.06</v>
+        <v>15.231</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>단계적 취득 차익</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="H105" s="22" t="n">
-        <v>0</v>
+        <v>2.831</v>
       </c>
       <c r="I105" s="22" t="n">
-        <v>0</v>
+        <v>39.175</v>
+      </c>
+      <c r="J105" s="22" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="K105" s="22" t="n">
+        <v>3.28</v>
       </c>
       <c r="L105" s="22" t="n">
-        <v>0</v>
+        <v>3.107</v>
       </c>
       <c r="M105" s="22" t="n">
-        <v>0</v>
+        <v>2.802</v>
+      </c>
+      <c r="N105" s="22" t="n">
+        <v>3.991</v>
       </c>
       <c r="W105" s="22" t="n">
-        <v>0</v>
+        <v>39.175</v>
       </c>
       <c r="X105" s="22" t="n">
-        <v>0</v>
+        <v>2.802</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>특별이익 합계</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="H106" s="22" t="n">
-        <v>8.991</v>
+        <v>129.545</v>
       </c>
       <c r="I106" s="22" t="n">
-        <v>3.527</v>
+        <v>232.364</v>
       </c>
       <c r="J106" s="22" t="n">
-        <v>3.061</v>
+        <v>215.703</v>
       </c>
       <c r="K106" s="22" t="n">
-        <v>41.665</v>
+        <v>130.992</v>
       </c>
       <c r="L106" s="22" t="n">
-        <v>2.408</v>
+        <v>157.253</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>1.06</v>
+        <v>238.679</v>
       </c>
       <c r="N106" s="22" t="n">
-        <v>0.917</v>
+        <v>257.272</v>
       </c>
       <c r="W106" s="22" t="n">
-        <v>3.527</v>
+        <v>232.364</v>
       </c>
       <c r="X106" s="22" t="n">
-        <v>1.06</v>
+        <v>238.679</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="H107" s="22" t="n">
-        <v>1.535</v>
-      </c>
-      <c r="I107" s="22" t="n">
-        <v>2.621</v>
-      </c>
-      <c r="J107" s="22" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="K107" s="22" t="n">
-        <v>3.326</v>
-      </c>
-      <c r="L107" s="22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="M107" s="22" t="n">
-        <v>6.141</v>
-      </c>
-      <c r="N107" s="22" t="n">
-        <v>11.954</v>
-      </c>
-      <c r="W107" s="22" t="n">
-        <v>2.621</v>
-      </c>
-      <c r="X107" s="22" t="n">
-        <v>6.141</v>
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>1293.958</v>
+      </c>
+      <c r="I107" s="12" t="n">
+        <v>-241.142</v>
+      </c>
+      <c r="J107" s="12" t="n">
+        <v>986.351</v>
+      </c>
+      <c r="K107" s="12" t="n">
+        <v>1624.342</v>
+      </c>
+      <c r="L107" s="12" t="n">
+        <v>1439.969</v>
+      </c>
+      <c r="M107" s="12" t="n">
+        <v>-104.026</v>
+      </c>
+      <c r="N107" s="12" t="n">
+        <v>1353.702</v>
+      </c>
+      <c r="W107" s="12" t="n">
+        <v>-241.142</v>
+      </c>
+      <c r="X107" s="12" t="n">
+        <v>-104.026</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="I108" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" s="22" t="n">
-        <v>0</v>
+      <c r="A108" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="H108" s="17">
+        <f>IF(OR(H107="",D107=""),"",IF(D107&lt;=0,"",IFERROR(H107/D107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I108" s="17">
+        <f>IF(OR(I107="",E107=""),"",IF(E107&lt;=0,"",IFERROR(I107/E107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J108" s="17">
+        <f>IF(OR(J107="",F107=""),"",IF(F107&lt;=0,"",IFERROR(J107/F107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K108" s="17">
+        <f>IF(OR(K107="",G107=""),"",IF(G107&lt;=0,"",IFERROR(K107/G107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L108" s="17">
+        <f>IF(OR(L107="",H107=""),"",IF(H107&lt;=0,"",IFERROR(L107/H107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M108" s="17">
+        <f>IF(OR(M107="",I107=""),"",IF(I107&lt;=0,"",IFERROR(M107/I107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N108" s="17">
+        <f>IF(OR(N107="",J107=""),"",IF(J107&lt;=0,"",IFERROR(N107/J107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W108" s="17">
+        <f>IF(OR(W107="",V107=""),"",IF(V107&lt;=0,"",IFERROR(W107/V107-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X108" s="17">
+        <f>IF(OR(X107="",W107=""),"",IF(W107&lt;=0,"",IFERROR(X107/W107-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
+          <t>고정자산 매각이익</t>
         </is>
       </c>
       <c r="H109" s="22" t="n">
-        <v>1.535</v>
+        <v>8.991</v>
       </c>
       <c r="I109" s="22" t="n">
-        <v>2.621</v>
+        <v>3.527</v>
       </c>
       <c r="J109" s="22" t="n">
-        <v>0.359</v>
+        <v>3.061</v>
       </c>
       <c r="K109" s="22" t="n">
-        <v>3.326</v>
+        <v>2.31</v>
       </c>
       <c r="L109" s="22" t="n">
-        <v>29.017</v>
+        <v>2.408</v>
       </c>
       <c r="M109" s="22" t="n">
-        <v>6.141</v>
+        <v>1.06</v>
       </c>
       <c r="N109" s="22" t="n">
-        <v>11.954</v>
+        <v>0.917</v>
       </c>
       <c r="W109" s="22" t="n">
-        <v>2.621</v>
+        <v>3.527</v>
       </c>
       <c r="X109" s="22" t="n">
-        <v>6.141</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="H110" s="12" t="n">
-        <v>1301.414</v>
-      </c>
-      <c r="I110" s="12" t="n">
-        <v>-240.236</v>
-      </c>
-      <c r="J110" s="12" t="n">
-        <v>989.053</v>
-      </c>
-      <c r="K110" s="12" t="n">
-        <v>1662.681</v>
-      </c>
-      <c r="L110" s="12" t="n">
-        <v>1413.36</v>
-      </c>
-      <c r="M110" s="12" t="n">
-        <v>-109.107</v>
-      </c>
-      <c r="N110" s="12" t="n">
-        <v>1342.666</v>
-      </c>
-      <c r="W110" s="12" t="n">
-        <v>-240.236</v>
-      </c>
-      <c r="X110" s="12" t="n">
-        <v>-109.107</v>
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>단계적 취득 차익</t>
+        </is>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>특별이익 합계</t>
         </is>
       </c>
       <c r="H111" s="22" t="n">
-        <v>187.36</v>
+        <v>8.991</v>
       </c>
       <c r="I111" s="22" t="n">
-        <v>14.533</v>
+        <v>3.527</v>
       </c>
       <c r="J111" s="22" t="n">
-        <v>207.892</v>
+        <v>3.061</v>
       </c>
       <c r="K111" s="22" t="n">
-        <v>778.827</v>
+        <v>41.665</v>
       </c>
       <c r="L111" s="22" t="n">
-        <v>256.77</v>
+        <v>2.408</v>
       </c>
       <c r="M111" s="22" t="n">
-        <v>80.92</v>
+        <v>1.06</v>
       </c>
       <c r="N111" s="22" t="n">
-        <v>242.336</v>
+        <v>0.917</v>
       </c>
       <c r="W111" s="22" t="n">
-        <v>14.533</v>
+        <v>3.527</v>
       </c>
       <c r="X111" s="22" t="n">
-        <v>80.92</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="H112" s="22" t="n">
-        <v>244.92</v>
+        <v>1.535</v>
       </c>
       <c r="I112" s="22" t="n">
-        <v>-197.908</v>
+        <v>2.621</v>
       </c>
       <c r="J112" s="22" t="n">
-        <v>133.204</v>
+        <v>0.359</v>
       </c>
       <c r="K112" s="22" t="n">
-        <v>-226.941</v>
+        <v>3.326</v>
       </c>
       <c r="L112" s="22" t="n">
-        <v>182.353</v>
+        <v>2.83</v>
       </c>
       <c r="M112" s="22" t="n">
-        <v>-274.473</v>
+        <v>6.141</v>
       </c>
       <c r="N112" s="22" t="n">
-        <v>215.69</v>
+        <v>11.954</v>
       </c>
       <c r="W112" s="22" t="n">
-        <v>-197.908</v>
+        <v>2.621</v>
       </c>
       <c r="X112" s="22" t="n">
-        <v>-274.473</v>
+        <v>6.141</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
-        </is>
-      </c>
-      <c r="H113" s="22" t="n">
-        <v>432.28</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="I113" s="22" t="n">
-        <v>-183.376</v>
-      </c>
-      <c r="J113" s="22" t="n">
-        <v>341.096</v>
-      </c>
-      <c r="K113" s="22" t="n">
-        <v>551.885</v>
-      </c>
-      <c r="L113" s="22" t="n">
-        <v>439.124</v>
+        <v>0</v>
       </c>
       <c r="M113" s="22" t="n">
-        <v>-193.554</v>
-      </c>
-      <c r="N113" s="22" t="n">
-        <v>458.026</v>
+        <v>0</v>
       </c>
       <c r="W113" s="22" t="n">
-        <v>-183.376</v>
+        <v>0</v>
       </c>
       <c r="X113" s="22" t="n">
-        <v>-193.554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H114" s="12" t="n">
-        <v>869.135</v>
-      </c>
-      <c r="I114" s="12" t="n">
-        <v>-56.861</v>
-      </c>
-      <c r="J114" s="12" t="n">
-        <v>647.956</v>
-      </c>
-      <c r="K114" s="12" t="n">
-        <v>1110.796</v>
-      </c>
-      <c r="L114" s="12" t="n">
-        <v>974.236</v>
-      </c>
-      <c r="M114" s="12" t="n">
-        <v>84.44799999999999</v>
-      </c>
-      <c r="N114" s="12" t="n">
-        <v>884.639</v>
-      </c>
-      <c r="W114" s="12" t="n">
-        <v>-56.861</v>
-      </c>
-      <c r="X114" s="12" t="n">
-        <v>84.44799999999999</v>
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="H114" s="22" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="I114" s="22" t="n">
+        <v>2.621</v>
+      </c>
+      <c r="J114" s="22" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="K114" s="22" t="n">
+        <v>3.326</v>
+      </c>
+      <c r="L114" s="22" t="n">
+        <v>29.017</v>
+      </c>
+      <c r="M114" s="22" t="n">
+        <v>6.141</v>
+      </c>
+      <c r="N114" s="22" t="n">
+        <v>11.954</v>
+      </c>
+      <c r="W114" s="22" t="n">
+        <v>2.621</v>
+      </c>
+      <c r="X114" s="22" t="n">
+        <v>6.141</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>1301.414</v>
+      </c>
+      <c r="I115" s="12" t="n">
+        <v>-240.236</v>
+      </c>
+      <c r="J115" s="12" t="n">
+        <v>989.053</v>
+      </c>
+      <c r="K115" s="12" t="n">
+        <v>1662.681</v>
+      </c>
+      <c r="L115" s="12" t="n">
+        <v>1413.36</v>
+      </c>
+      <c r="M115" s="12" t="n">
+        <v>-109.107</v>
+      </c>
+      <c r="N115" s="12" t="n">
+        <v>1342.666</v>
+      </c>
+      <c r="W115" s="12" t="n">
+        <v>-240.236</v>
+      </c>
+      <c r="X115" s="12" t="n">
+        <v>-109.107</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="H116" s="22" t="n">
+        <v>187.36</v>
+      </c>
+      <c r="I116" s="22" t="n">
+        <v>14.533</v>
+      </c>
+      <c r="J116" s="22" t="n">
+        <v>207.892</v>
+      </c>
+      <c r="K116" s="22" t="n">
+        <v>778.827</v>
+      </c>
+      <c r="L116" s="22" t="n">
+        <v>256.77</v>
+      </c>
+      <c r="M116" s="22" t="n">
+        <v>80.92</v>
+      </c>
+      <c r="N116" s="22" t="n">
+        <v>242.336</v>
+      </c>
+      <c r="W116" s="22" t="n">
+        <v>14.533</v>
+      </c>
+      <c r="X116" s="22" t="n">
+        <v>80.92</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="H117" s="22" t="n">
+        <v>244.92</v>
+      </c>
+      <c r="I117" s="22" t="n">
+        <v>-197.908</v>
+      </c>
+      <c r="J117" s="22" t="n">
+        <v>133.204</v>
+      </c>
+      <c r="K117" s="22" t="n">
+        <v>-226.941</v>
+      </c>
+      <c r="L117" s="22" t="n">
+        <v>182.353</v>
+      </c>
+      <c r="M117" s="22" t="n">
+        <v>-274.473</v>
+      </c>
+      <c r="N117" s="22" t="n">
+        <v>215.69</v>
+      </c>
+      <c r="W117" s="22" t="n">
+        <v>-197.908</v>
+      </c>
+      <c r="X117" s="22" t="n">
+        <v>-274.473</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="H118" s="22" t="n">
+        <v>432.28</v>
+      </c>
+      <c r="I118" s="22" t="n">
+        <v>-183.376</v>
+      </c>
+      <c r="J118" s="22" t="n">
+        <v>341.096</v>
+      </c>
+      <c r="K118" s="22" t="n">
+        <v>551.885</v>
+      </c>
+      <c r="L118" s="22" t="n">
+        <v>439.124</v>
+      </c>
+      <c r="M118" s="22" t="n">
+        <v>-193.554</v>
+      </c>
+      <c r="N118" s="22" t="n">
+        <v>458.026</v>
+      </c>
+      <c r="W118" s="22" t="n">
+        <v>-183.376</v>
+      </c>
+      <c r="X118" s="22" t="n">
+        <v>-193.554</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>869.135</v>
+      </c>
+      <c r="I119" s="12" t="n">
+        <v>-56.861</v>
+      </c>
+      <c r="J119" s="12" t="n">
+        <v>647.956</v>
+      </c>
+      <c r="K119" s="12" t="n">
+        <v>1110.796</v>
+      </c>
+      <c r="L119" s="12" t="n">
+        <v>974.236</v>
+      </c>
+      <c r="M119" s="12" t="n">
+        <v>84.44799999999999</v>
+      </c>
+      <c r="N119" s="12" t="n">
+        <v>884.639</v>
+      </c>
+      <c r="W119" s="12" t="n">
+        <v>-56.861</v>
+      </c>
+      <c r="X119" s="12" t="n">
+        <v>84.44799999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="H120" s="17">
+        <f>IF(OR(H119="",D119=""),"",IF(D119&lt;=0,"",IFERROR(H119/D119-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I120" s="17">
+        <f>IF(OR(I119="",E119=""),"",IF(E119&lt;=0,"",IFERROR(I119/E119-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J120" s="17">
+        <f>IF(OR(J119="",F119=""),"",IF(F119&lt;=0,"",IFERROR(J119/F119-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K120" s="17">
+        <f>IF(OR(K119="",G119=""),"",IF(G119&lt;=0,"",IFERROR(K119/G119-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L120" s="17">
+        <f>IF(OR(L119="",H119=""),"",IF(H119&lt;=0,"",IFERROR(L119/H119-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M120" s="17">
+        <f>IF(OR(M119="",I119=""),"",IF(I119&lt;=0,"",IFERROR(M119/I119-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N120" s="17">
+        <f>IF(OR(N119="",J119=""),"",IF(J119&lt;=0,"",IFERROR(N119/J119-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W120" s="17">
+        <f>IF(OR(W119="",V119=""),"",IF(V119&lt;=0,"",IFERROR(W119/V119-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X120" s="17">
+        <f>IF(OR(X119="",W119=""),"",IF(W119&lt;=0,"",IFERROR(X119/W119-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
           <t>비지배주주 당기순손실</t>
         </is>
       </c>
-      <c r="H115" s="12" t="n">
+      <c r="H121" s="12" t="n">
         <v>-35.62</v>
       </c>
-      <c r="I115" s="12" t="n">
+      <c r="I121" s="12" t="n">
         <v>-40.224</v>
       </c>
-      <c r="J115" s="12" t="n">
+      <c r="J121" s="12" t="n">
         <v>-42.353</v>
       </c>
-      <c r="K115" s="12" t="n">
+      <c r="K121" s="12" t="n">
         <v>-36.713</v>
       </c>
-      <c r="L115" s="12" t="n">
+      <c r="L121" s="12" t="n">
         <v>-2.439</v>
       </c>
-      <c r="M115" s="12" t="n">
+      <c r="M121" s="12" t="n">
         <v>-2.128</v>
       </c>
-      <c r="N115" s="12" t="n">
+      <c r="N121" s="12" t="n">
         <v>-3.461</v>
       </c>
-      <c r="W115" s="12" t="n">
+      <c r="W121" s="12" t="n">
         <v>-40.224</v>
       </c>
-      <c r="X115" s="12" t="n">
+      <c r="X121" s="12" t="n">
         <v>-2.128</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="9" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>지배주주 순이익</t>
         </is>
       </c>
-      <c r="H116" s="12" t="n">
+      <c r="H122" s="12" t="n">
         <v>904.755</v>
       </c>
-      <c r="I116" s="12" t="n">
+      <c r="I122" s="12" t="n">
         <v>-16.637</v>
       </c>
-      <c r="J116" s="12" t="n">
+      <c r="J122" s="12" t="n">
         <v>690.309</v>
       </c>
-      <c r="K116" s="12" t="n">
+      <c r="K122" s="12" t="n">
         <v>1147.51</v>
       </c>
-      <c r="L116" s="12" t="n">
+      <c r="L122" s="12" t="n">
         <v>976.674</v>
       </c>
-      <c r="M116" s="12" t="n">
+      <c r="M122" s="12" t="n">
         <v>86.57599999999999</v>
       </c>
-      <c r="N116" s="12" t="n">
+      <c r="N122" s="12" t="n">
         <v>888.1</v>
       </c>
-      <c r="W116" s="12" t="n">
+      <c r="W122" s="12" t="n">
         <v>-16.637</v>
       </c>
-      <c r="X116" s="12" t="n">
+      <c r="X122" s="12" t="n">
         <v>86.57599999999999</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="18" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="H123" s="17">
+        <f>IF(OR(H122="",D122=""),"",IF(D122&lt;=0,"",IFERROR(H122/D122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I123" s="17">
+        <f>IF(OR(I122="",E122=""),"",IF(E122&lt;=0,"",IFERROR(I122/E122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J123" s="17">
+        <f>IF(OR(J122="",F122=""),"",IF(F122&lt;=0,"",IFERROR(J122/F122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K123" s="17">
+        <f>IF(OR(K122="",G122=""),"",IF(G122&lt;=0,"",IFERROR(K122/G122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L123" s="17">
+        <f>IF(OR(L122="",H122=""),"",IF(H122&lt;=0,"",IFERROR(L122/H122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M123" s="17">
+        <f>IF(OR(M122="",I122=""),"",IF(I122&lt;=0,"",IFERROR(M122/I122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N123" s="17">
+        <f>IF(OR(N122="",J122=""),"",IF(J122&lt;=0,"",IFERROR(N122/J122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W123" s="17">
+        <f>IF(OR(W122="",V122=""),"",IF(V122&lt;=0,"",IFERROR(W122/V122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X123" s="17">
+        <f>IF(OR(X122="",W122=""),"",IF(W122&lt;=0,"",IFERROR(X122/W122-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="18" t="inlineStr">
         <is>
           <t>포괄손익 · 전 항목</t>
         </is>
       </c>
-      <c r="B118" s="44" t="inlineStr">
+      <c r="B125" s="44" t="inlineStr">
         <is>
           <t>분기 = 3개월 단독</t>
         </is>
       </c>
-      <c r="C118" s="18" t="n"/>
-      <c r="D118" s="18" t="n"/>
-      <c r="E118" s="18" t="n"/>
-      <c r="F118" s="18" t="n"/>
-      <c r="G118" s="18" t="n"/>
-      <c r="H118" s="18" t="n"/>
-      <c r="I118" s="18" t="n"/>
-      <c r="J118" s="18" t="n"/>
-      <c r="K118" s="18" t="n"/>
-      <c r="L118" s="18" t="n"/>
-      <c r="M118" s="18" t="n"/>
-      <c r="N118" s="18" t="n"/>
-      <c r="O118" s="18" t="n"/>
-      <c r="P118" s="18" t="n"/>
-      <c r="Q118" s="18" t="n"/>
-      <c r="R118" s="18" t="n"/>
-      <c r="S118" s="18" t="n"/>
-      <c r="T118" s="18" t="n"/>
-      <c r="U118" s="18" t="n"/>
-      <c r="V118" s="18" t="n"/>
-      <c r="W118" s="18" t="n"/>
-      <c r="X118" s="18" t="n"/>
-      <c r="Y118" s="18" t="n"/>
-      <c r="Z118" s="18" t="n"/>
-      <c r="AA118" s="18" t="n"/>
-      <c r="AB118" s="18" t="n"/>
-      <c r="AC118" s="18" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="C125" s="18" t="n"/>
+      <c r="D125" s="18" t="n"/>
+      <c r="E125" s="18" t="n"/>
+      <c r="F125" s="18" t="n"/>
+      <c r="G125" s="18" t="n"/>
+      <c r="H125" s="18" t="n"/>
+      <c r="I125" s="18" t="n"/>
+      <c r="J125" s="18" t="n"/>
+      <c r="K125" s="18" t="n"/>
+      <c r="L125" s="18" t="n"/>
+      <c r="M125" s="18" t="n"/>
+      <c r="N125" s="18" t="n"/>
+      <c r="O125" s="18" t="n"/>
+      <c r="P125" s="18" t="n"/>
+      <c r="Q125" s="18" t="n"/>
+      <c r="R125" s="18" t="n"/>
+      <c r="S125" s="18" t="n"/>
+      <c r="T125" s="18" t="n"/>
+      <c r="U125" s="18" t="n"/>
+      <c r="V125" s="18" t="n"/>
+      <c r="W125" s="18" t="n"/>
+      <c r="X125" s="18" t="n"/>
+      <c r="Y125" s="18" t="n"/>
+      <c r="Z125" s="18" t="n"/>
+      <c r="AA125" s="18" t="n"/>
+      <c r="AB125" s="18" t="n"/>
+      <c r="AC125" s="18" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B126" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E126" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="F126" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="G126" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="H126" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="I126" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J119" s="5" t="inlineStr">
+      <c r="J126" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K119" s="5" t="inlineStr">
+      <c r="K126" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L119" s="5" t="inlineStr">
+      <c r="L126" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M119" s="5" t="inlineStr">
+      <c r="M126" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N119" s="5" t="inlineStr">
+      <c r="N126" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O119" s="5" t="inlineStr">
+      <c r="O126" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P119" s="5" t="inlineStr">
+      <c r="P126" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q119" s="5" t="inlineStr">
+      <c r="Q126" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R119" s="5" t="inlineStr">
+      <c r="R126" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S119" s="5" t="inlineStr">
+      <c r="S126" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T119" s="5" t="inlineStr">
+      <c r="T126" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U119" s="5" t="inlineStr">
+      <c r="U126" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V119" s="5" t="inlineStr">
+      <c r="V126" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W119" s="5" t="inlineStr">
+      <c r="W126" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X119" s="5" t="inlineStr">
+      <c r="X126" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y119" s="5" t="inlineStr">
+      <c r="Y126" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z119" s="5" t="inlineStr">
+      <c r="Z126" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA119" s="5" t="inlineStr">
+      <c r="AA126" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB119" s="5" t="inlineStr">
+      <c r="AB126" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC119" s="5" t="inlineStr">
+      <c r="AC126" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H120" s="12" t="n">
-        <v>869.135</v>
-      </c>
-      <c r="I120" s="12" t="n">
-        <v>-56.861</v>
-      </c>
-      <c r="J120" s="12" t="n">
-        <v>647.956</v>
-      </c>
-      <c r="K120" s="12" t="n">
-        <v>1110.796</v>
-      </c>
-      <c r="L120" s="12" t="n">
-        <v>974.236</v>
-      </c>
-      <c r="M120" s="12" t="n">
-        <v>84.44799999999999</v>
-      </c>
-      <c r="N120" s="12" t="n">
-        <v>884.639</v>
-      </c>
-      <c r="W120" s="12" t="n">
-        <v>-56.861</v>
-      </c>
-      <c r="X120" s="12" t="n">
-        <v>84.44799999999999</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="20" t="inlineStr">
-        <is>
-          <t>기타유가증권 평가차액</t>
-        </is>
-      </c>
-      <c r="H121" s="22" t="n">
-        <v>-3.196</v>
-      </c>
-      <c r="I121" s="22" t="n">
-        <v>-6.073</v>
-      </c>
-      <c r="J121" s="22" t="n">
-        <v>34.029</v>
-      </c>
-      <c r="K121" s="22" t="n">
-        <v>6.769</v>
-      </c>
-      <c r="L121" s="22" t="n">
-        <v>38.099</v>
-      </c>
-      <c r="M121" s="22" t="n">
-        <v>-2.654</v>
-      </c>
-      <c r="N121" s="22" t="n">
-        <v>38.52</v>
-      </c>
-      <c r="W121" s="22" t="n">
-        <v>-6.073</v>
-      </c>
-      <c r="X121" s="22" t="n">
-        <v>-2.654</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="20" t="inlineStr">
-        <is>
-          <t>이연헤지손익</t>
-        </is>
-      </c>
-      <c r="H122" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="22" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="J122" s="22" t="n">
-        <v>2.011</v>
-      </c>
-      <c r="K122" s="22" t="n">
-        <v>1.811</v>
-      </c>
-      <c r="L122" s="22" t="n">
-        <v>4.826</v>
-      </c>
-      <c r="M122" s="22" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="N122" s="22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W122" s="22" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="X122" s="22" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="20" t="inlineStr">
-        <is>
-          <t>해외사업환산조정</t>
-        </is>
-      </c>
-      <c r="H123" s="22" t="n">
-        <v>19.447</v>
-      </c>
-      <c r="I123" s="22" t="n">
-        <v>-80.622</v>
-      </c>
-      <c r="J123" s="22" t="n">
-        <v>3.313</v>
-      </c>
-      <c r="K123" s="22" t="n">
-        <v>-38.633</v>
-      </c>
-      <c r="L123" s="22" t="n">
-        <v>-14.931</v>
-      </c>
-      <c r="M123" s="22" t="n">
-        <v>21.084</v>
-      </c>
-      <c r="N123" s="22" t="n">
-        <v>-2.743</v>
-      </c>
-      <c r="W123" s="22" t="n">
-        <v>-80.622</v>
-      </c>
-      <c r="X123" s="22" t="n">
-        <v>21.084</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여 조정액</t>
-        </is>
-      </c>
-      <c r="H124" s="22" t="n">
-        <v>2.435</v>
-      </c>
-      <c r="I124" s="22" t="n">
-        <v>34.389</v>
-      </c>
-      <c r="J124" s="22" t="n">
-        <v>0.962</v>
-      </c>
-      <c r="K124" s="22" t="n">
-        <v>0.963</v>
-      </c>
-      <c r="L124" s="22" t="n">
-        <v>0.962</v>
-      </c>
-      <c r="M124" s="22" t="n">
-        <v>99.56999999999999</v>
-      </c>
-      <c r="N124" s="22" t="n">
-        <v>-3.865</v>
-      </c>
-      <c r="W124" s="22" t="n">
-        <v>34.389</v>
-      </c>
-      <c r="X124" s="22" t="n">
-        <v>99.56999999999999</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>지분법 적용회사 지분 해당액</t>
-        </is>
-      </c>
-      <c r="H125" s="22" t="n">
-        <v>3.206</v>
-      </c>
-      <c r="I125" s="22" t="n">
-        <v>-1.211</v>
-      </c>
-      <c r="J125" s="22" t="n">
-        <v>-0.428</v>
-      </c>
-      <c r="K125" s="22" t="n">
-        <v>6.191</v>
-      </c>
-      <c r="L125" s="22" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="M125" s="22" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="N125" s="22" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>-1.211</v>
-      </c>
-      <c r="X125" s="22" t="n">
-        <v>0.871</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="H126" s="22" t="n">
-        <v>21.891</v>
-      </c>
-      <c r="I126" s="22" t="n">
-        <v>-56.318</v>
-      </c>
-      <c r="J126" s="22" t="n">
-        <v>39.888</v>
-      </c>
-      <c r="K126" s="22" t="n">
-        <v>-22.899</v>
-      </c>
-      <c r="L126" s="22" t="n">
-        <v>29.24</v>
-      </c>
-      <c r="M126" s="22" t="n">
-        <v>118.955</v>
-      </c>
-      <c r="N126" s="22" t="n">
-        <v>33.849</v>
-      </c>
-      <c r="W126" s="22" t="n">
-        <v>-56.318</v>
-      </c>
-      <c r="X126" s="22" t="n">
-        <v>118.955</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="n">
+        <v>869.135</v>
+      </c>
+      <c r="I127" s="12" t="n">
+        <v>-56.861</v>
+      </c>
+      <c r="J127" s="12" t="n">
+        <v>647.956</v>
+      </c>
+      <c r="K127" s="12" t="n">
+        <v>1110.796</v>
+      </c>
+      <c r="L127" s="12" t="n">
+        <v>974.236</v>
+      </c>
+      <c r="M127" s="12" t="n">
+        <v>84.44799999999999</v>
+      </c>
+      <c r="N127" s="12" t="n">
+        <v>884.639</v>
+      </c>
+      <c r="W127" s="12" t="n">
+        <v>-56.861</v>
+      </c>
+      <c r="X127" s="12" t="n">
+        <v>84.44799999999999</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>기타유가증권 평가차액</t>
+        </is>
+      </c>
+      <c r="H128" s="22" t="n">
+        <v>-3.196</v>
+      </c>
+      <c r="I128" s="22" t="n">
+        <v>-6.073</v>
+      </c>
+      <c r="J128" s="22" t="n">
+        <v>34.029</v>
+      </c>
+      <c r="K128" s="22" t="n">
+        <v>6.769</v>
+      </c>
+      <c r="L128" s="22" t="n">
+        <v>38.099</v>
+      </c>
+      <c r="M128" s="22" t="n">
+        <v>-2.654</v>
+      </c>
+      <c r="N128" s="22" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="W128" s="22" t="n">
+        <v>-6.073</v>
+      </c>
+      <c r="X128" s="22" t="n">
+        <v>-2.654</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20" t="inlineStr">
+        <is>
+          <t>이연헤지손익</t>
+        </is>
+      </c>
+      <c r="H129" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="22" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="J129" s="22" t="n">
+        <v>2.011</v>
+      </c>
+      <c r="K129" s="22" t="n">
+        <v>1.811</v>
+      </c>
+      <c r="L129" s="22" t="n">
+        <v>4.826</v>
+      </c>
+      <c r="M129" s="22" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="N129" s="22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W129" s="22" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="X129" s="22" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>해외사업환산조정</t>
+        </is>
+      </c>
+      <c r="H130" s="22" t="n">
+        <v>19.447</v>
+      </c>
+      <c r="I130" s="22" t="n">
+        <v>-80.622</v>
+      </c>
+      <c r="J130" s="22" t="n">
+        <v>3.313</v>
+      </c>
+      <c r="K130" s="22" t="n">
+        <v>-38.633</v>
+      </c>
+      <c r="L130" s="22" t="n">
+        <v>-14.931</v>
+      </c>
+      <c r="M130" s="22" t="n">
+        <v>21.084</v>
+      </c>
+      <c r="N130" s="22" t="n">
+        <v>-2.743</v>
+      </c>
+      <c r="W130" s="22" t="n">
+        <v>-80.622</v>
+      </c>
+      <c r="X130" s="22" t="n">
+        <v>21.084</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="20" t="inlineStr">
+        <is>
+          <t>퇴직급여 조정액</t>
+        </is>
+      </c>
+      <c r="H131" s="22" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="I131" s="22" t="n">
+        <v>34.389</v>
+      </c>
+      <c r="J131" s="22" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="K131" s="22" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="L131" s="22" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="M131" s="22" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="N131" s="22" t="n">
+        <v>-3.865</v>
+      </c>
+      <c r="W131" s="22" t="n">
+        <v>34.389</v>
+      </c>
+      <c r="X131" s="22" t="n">
+        <v>99.56999999999999</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>지분법 적용회사 지분 해당액</t>
+        </is>
+      </c>
+      <c r="H132" s="22" t="n">
+        <v>3.206</v>
+      </c>
+      <c r="I132" s="22" t="n">
+        <v>-1.211</v>
+      </c>
+      <c r="J132" s="22" t="n">
+        <v>-0.428</v>
+      </c>
+      <c r="K132" s="22" t="n">
+        <v>6.191</v>
+      </c>
+      <c r="L132" s="22" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="M132" s="22" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="N132" s="22" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="W132" s="22" t="n">
+        <v>-1.211</v>
+      </c>
+      <c r="X132" s="22" t="n">
+        <v>0.871</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="inlineStr">
+        <is>
+          <t>기타포괄손익 합계</t>
+        </is>
+      </c>
+      <c r="H133" s="22" t="n">
+        <v>21.891</v>
+      </c>
+      <c r="I133" s="22" t="n">
+        <v>-56.318</v>
+      </c>
+      <c r="J133" s="22" t="n">
+        <v>39.888</v>
+      </c>
+      <c r="K133" s="22" t="n">
+        <v>-22.899</v>
+      </c>
+      <c r="L133" s="22" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="M133" s="22" t="n">
+        <v>118.955</v>
+      </c>
+      <c r="N133" s="22" t="n">
+        <v>33.849</v>
+      </c>
+      <c r="W133" s="22" t="n">
+        <v>-56.318</v>
+      </c>
+      <c r="X133" s="22" t="n">
+        <v>118.955</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
           <t>포괄이익</t>
         </is>
       </c>
-      <c r="H127" s="12" t="n">
+      <c r="H134" s="12" t="n">
         <v>891.026</v>
       </c>
-      <c r="I127" s="12" t="n">
+      <c r="I134" s="12" t="n">
         <v>-113.179</v>
       </c>
-      <c r="J127" s="12" t="n">
+      <c r="J134" s="12" t="n">
         <v>687.845</v>
       </c>
-      <c r="K127" s="12" t="n">
+      <c r="K134" s="12" t="n">
         <v>1087.897</v>
       </c>
-      <c r="L127" s="12" t="n">
+      <c r="L134" s="12" t="n">
         <v>1003.476</v>
       </c>
-      <c r="M127" s="12" t="n">
+      <c r="M134" s="12" t="n">
         <v>203.402</v>
       </c>
-      <c r="N127" s="12" t="n">
+      <c r="N134" s="12" t="n">
         <v>918.4880000000001</v>
       </c>
-      <c r="W127" s="12" t="n">
+      <c r="W134" s="12" t="n">
         <v>-113.179</v>
       </c>
-      <c r="X127" s="12" t="n">
+      <c r="X134" s="12" t="n">
         <v>203.402</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="9" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="H128" s="12" t="n">
+      <c r="H135" s="12" t="n">
         <v>917.929</v>
       </c>
-      <c r="I128" s="12" t="n">
+      <c r="I135" s="12" t="n">
         <v>-55.597</v>
       </c>
-      <c r="J128" s="12" t="n">
+      <c r="J135" s="12" t="n">
         <v>733.215</v>
       </c>
-      <c r="K128" s="12" t="n">
+      <c r="K135" s="12" t="n">
         <v>1124.452</v>
       </c>
-      <c r="L128" s="12" t="n">
+      <c r="L135" s="12" t="n">
         <v>1005.141</v>
       </c>
-      <c r="M128" s="12" t="n">
+      <c r="M135" s="12" t="n">
         <v>205.493</v>
       </c>
-      <c r="N128" s="12" t="n">
+      <c r="N135" s="12" t="n">
         <v>922.317</v>
       </c>
-      <c r="W128" s="12" t="n">
+      <c r="W135" s="12" t="n">
         <v>-55.597</v>
       </c>
-      <c r="X128" s="12" t="n">
+      <c r="X135" s="12" t="n">
         <v>205.493</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="9" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
         <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="H129" s="12" t="n">
+      <c r="H136" s="12" t="n">
         <v>-26.903</v>
       </c>
-      <c r="I129" s="12" t="n">
+      <c r="I136" s="12" t="n">
         <v>-57.582</v>
       </c>
-      <c r="J129" s="12" t="n">
+      <c r="J136" s="12" t="n">
         <v>-45.37</v>
       </c>
-      <c r="K129" s="12" t="n">
+      <c r="K136" s="12" t="n">
         <v>-36.555</v>
       </c>
-      <c r="L129" s="12" t="n">
+      <c r="L136" s="12" t="n">
         <v>-1.664</v>
       </c>
-      <c r="M129" s="12" t="n">
+      <c r="M136" s="12" t="n">
         <v>-2.091</v>
       </c>
-      <c r="N129" s="12" t="n">
+      <c r="N136" s="12" t="n">
         <v>-3.828</v>
       </c>
-      <c r="W129" s="12" t="n">
+      <c r="W136" s="12" t="n">
         <v>-57.582</v>
       </c>
-      <c r="X129" s="12" t="n">
+      <c r="X136" s="12" t="n">
         <v>-2.091</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="18" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B131" s="44" t="inlineStr">
+      <c r="B138" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C131" s="18" t="n"/>
-      <c r="D131" s="18" t="n"/>
-      <c r="E131" s="18" t="n"/>
-      <c r="F131" s="18" t="n"/>
-      <c r="G131" s="18" t="n"/>
-      <c r="H131" s="18" t="n"/>
-      <c r="I131" s="18" t="n"/>
-      <c r="J131" s="18" t="n"/>
-      <c r="K131" s="18" t="n"/>
-      <c r="L131" s="18" t="n"/>
-      <c r="M131" s="18" t="n"/>
-      <c r="N131" s="18" t="n"/>
-      <c r="O131" s="18" t="n"/>
-      <c r="P131" s="18" t="n"/>
-      <c r="Q131" s="18" t="n"/>
-      <c r="R131" s="18" t="n"/>
-      <c r="S131" s="18" t="n"/>
-      <c r="T131" s="18" t="n"/>
-      <c r="U131" s="18" t="n"/>
-      <c r="V131" s="18" t="n"/>
-      <c r="W131" s="18" t="n"/>
-      <c r="X131" s="18" t="n"/>
-      <c r="Y131" s="18" t="n"/>
-      <c r="Z131" s="18" t="n"/>
-      <c r="AA131" s="18" t="n"/>
-      <c r="AB131" s="18" t="n"/>
-      <c r="AC131" s="18" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
+      <c r="C138" s="18" t="n"/>
+      <c r="D138" s="18" t="n"/>
+      <c r="E138" s="18" t="n"/>
+      <c r="F138" s="18" t="n"/>
+      <c r="G138" s="18" t="n"/>
+      <c r="H138" s="18" t="n"/>
+      <c r="I138" s="18" t="n"/>
+      <c r="J138" s="18" t="n"/>
+      <c r="K138" s="18" t="n"/>
+      <c r="L138" s="18" t="n"/>
+      <c r="M138" s="18" t="n"/>
+      <c r="N138" s="18" t="n"/>
+      <c r="O138" s="18" t="n"/>
+      <c r="P138" s="18" t="n"/>
+      <c r="Q138" s="18" t="n"/>
+      <c r="R138" s="18" t="n"/>
+      <c r="S138" s="18" t="n"/>
+      <c r="T138" s="18" t="n"/>
+      <c r="U138" s="18" t="n"/>
+      <c r="V138" s="18" t="n"/>
+      <c r="W138" s="18" t="n"/>
+      <c r="X138" s="18" t="n"/>
+      <c r="Y138" s="18" t="n"/>
+      <c r="Z138" s="18" t="n"/>
+      <c r="AA138" s="18" t="n"/>
+      <c r="AB138" s="18" t="n"/>
+      <c r="AC138" s="18" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="B139" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C139" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
+      <c r="F139" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G132" s="5" t="inlineStr">
+      <c r="G139" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="H139" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I139" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J132" s="5" t="inlineStr">
+      <c r="J139" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K132" s="5" t="inlineStr">
+      <c r="K139" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L132" s="5" t="inlineStr">
+      <c r="L139" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M132" s="5" t="inlineStr">
+      <c r="M139" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N132" s="5" t="inlineStr">
+      <c r="N139" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O132" s="5" t="inlineStr">
+      <c r="O139" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P132" s="5" t="inlineStr">
+      <c r="P139" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q132" s="5" t="inlineStr">
+      <c r="Q139" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R132" s="5" t="inlineStr">
+      <c r="R139" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S132" s="5" t="inlineStr">
+      <c r="S139" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T132" s="5" t="inlineStr">
+      <c r="T139" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U132" s="5" t="inlineStr">
+      <c r="U139" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V132" s="5" t="inlineStr">
+      <c r="V139" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W132" s="5" t="inlineStr">
+      <c r="W139" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X132" s="5" t="inlineStr">
+      <c r="X139" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y132" s="5" t="inlineStr">
+      <c r="Y139" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z132" s="5" t="inlineStr">
+      <c r="Z139" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA132" s="5" t="inlineStr">
+      <c r="AA139" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB132" s="5" t="inlineStr">
+      <c r="AB139" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC132" s="5" t="inlineStr">
+      <c r="AC139" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="9" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="E133" s="12" t="n">
+      <c r="E140" s="12" t="n">
         <v>2794.627</v>
       </c>
-      <c r="G133" s="12" t="n">
+      <c r="G140" s="12" t="n">
         <v>2390.609</v>
       </c>
-      <c r="I133" s="12" t="n">
+      <c r="I140" s="12" t="n">
         <v>3451.787</v>
       </c>
-      <c r="K133" s="12" t="n">
+      <c r="K140" s="12" t="n">
         <v>2651.734</v>
       </c>
-      <c r="M133" s="12" t="n">
+      <c r="M140" s="12" t="n">
         <v>3955.987</v>
       </c>
-      <c r="V133" s="12" t="n">
+      <c r="V140" s="12" t="n">
         <v>2794.627</v>
       </c>
-      <c r="W133" s="12" t="n">
+      <c r="W140" s="12" t="n">
         <v>3451.787</v>
       </c>
-      <c r="X133" s="12" t="n">
+      <c r="X140" s="12" t="n">
         <v>3955.987</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E134" s="22" t="n">
-        <v>7467.171</v>
-      </c>
-      <c r="G134" s="22" t="n">
-        <v>3794.705</v>
-      </c>
-      <c r="I134" s="22" t="n">
-        <v>7864.63</v>
-      </c>
-      <c r="K134" s="22" t="n">
-        <v>4174.622</v>
-      </c>
-      <c r="M134" s="22" t="n">
-        <v>8714.097</v>
-      </c>
-      <c r="V134" s="22" t="n">
-        <v>7467.171</v>
-      </c>
-      <c r="W134" s="22" t="n">
-        <v>7864.63</v>
-      </c>
-      <c r="X134" s="22" t="n">
-        <v>8714.097</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="I135" s="22" t="n">
-        <v>4.129</v>
-      </c>
-      <c r="M135" s="22" t="n">
-        <v>30.213</v>
-      </c>
-      <c r="W135" s="22" t="n">
-        <v>4.129</v>
-      </c>
-      <c r="X135" s="22" t="n">
-        <v>30.213</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="20" t="inlineStr">
-        <is>
-          <t>렌털자산 취득</t>
-        </is>
-      </c>
-      <c r="E136" s="22" t="n">
-        <v>-6584.18</v>
-      </c>
-      <c r="G136" s="22" t="n">
-        <v>-3489.134</v>
-      </c>
-      <c r="I136" s="22" t="n">
-        <v>-9250.064</v>
-      </c>
-      <c r="K136" s="22" t="n">
-        <v>-3754.107</v>
-      </c>
-      <c r="M136" s="22" t="n">
-        <v>-9341.819</v>
-      </c>
-      <c r="V136" s="22" t="n">
-        <v>-6584.18</v>
-      </c>
-      <c r="W136" s="22" t="n">
-        <v>-9250.064</v>
-      </c>
-      <c r="X136" s="22" t="n">
-        <v>-9341.819</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="20" t="inlineStr">
-        <is>
-          <t>렌털자산 매각 원가대체</t>
-        </is>
-      </c>
-      <c r="E137" s="22" t="n">
-        <v>26.504</v>
-      </c>
-      <c r="G137" s="22" t="n">
-        <v>7.894</v>
-      </c>
-      <c r="I137" s="22" t="n">
-        <v>29.019</v>
-      </c>
-      <c r="K137" s="22" t="n">
-        <v>17.249</v>
-      </c>
-      <c r="M137" s="22" t="n">
-        <v>43.435</v>
-      </c>
-      <c r="V137" s="22" t="n">
-        <v>26.504</v>
-      </c>
-      <c r="W137" s="22" t="n">
-        <v>29.019</v>
-      </c>
-      <c r="X137" s="22" t="n">
-        <v>43.435</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="E138" s="22" t="n">
-        <v>79.681</v>
-      </c>
-      <c r="G138" s="22" t="n">
-        <v>73.45099999999999</v>
-      </c>
-      <c r="I138" s="22" t="n">
-        <v>55.414</v>
-      </c>
-      <c r="K138" s="22" t="n">
-        <v>134.958</v>
-      </c>
-      <c r="M138" s="22" t="n">
-        <v>132.662</v>
-      </c>
-      <c r="V138" s="22" t="n">
-        <v>79.681</v>
-      </c>
-      <c r="W138" s="22" t="n">
-        <v>55.414</v>
-      </c>
-      <c r="X138" s="22" t="n">
-        <v>132.662</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="E139" s="22" t="n">
-        <v>115.373</v>
-      </c>
-      <c r="G139" s="22" t="n">
-        <v>66.374</v>
-      </c>
-      <c r="I139" s="22" t="n">
-        <v>163.19</v>
-      </c>
-      <c r="K139" s="22" t="n">
-        <v>37.846</v>
-      </c>
-      <c r="M139" s="22" t="n">
-        <v>38.587</v>
-      </c>
-      <c r="V139" s="22" t="n">
-        <v>115.373</v>
-      </c>
-      <c r="W139" s="22" t="n">
-        <v>163.19</v>
-      </c>
-      <c r="X139" s="22" t="n">
-        <v>38.587</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여부채 증감</t>
-        </is>
-      </c>
-      <c r="E140" s="22" t="n">
-        <v>64.167</v>
-      </c>
-      <c r="G140" s="22" t="n">
-        <v>19.07</v>
-      </c>
-      <c r="I140" s="22" t="n">
-        <v>54.689</v>
-      </c>
-      <c r="K140" s="22" t="n">
-        <v>13.767</v>
-      </c>
-      <c r="M140" s="22" t="n">
-        <v>11.202</v>
-      </c>
-      <c r="V140" s="22" t="n">
-        <v>64.167</v>
-      </c>
-      <c r="W140" s="22" t="n">
-        <v>54.689</v>
-      </c>
-      <c r="X140" s="22" t="n">
-        <v>11.202</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>주식보상비용</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E141" s="22" t="n">
-        <v>58.768</v>
+        <v>7467.171</v>
       </c>
       <c r="G141" s="22" t="n">
-        <v>35.372</v>
+        <v>3794.705</v>
       </c>
       <c r="I141" s="22" t="n">
-        <v>75.566</v>
+        <v>7864.63</v>
       </c>
       <c r="K141" s="22" t="n">
-        <v>41.948</v>
+        <v>4174.622</v>
       </c>
       <c r="M141" s="22" t="n">
-        <v>88.355</v>
+        <v>8714.097</v>
       </c>
       <c r="V141" s="22" t="n">
-        <v>58.768</v>
+        <v>7467.171</v>
       </c>
       <c r="W141" s="22" t="n">
-        <v>75.566</v>
+        <v>7864.63</v>
       </c>
       <c r="X141" s="22" t="n">
-        <v>88.355</v>
+        <v>8714.097</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="E142" s="22" t="n">
-        <v>-13.62</v>
-      </c>
-      <c r="G142" s="22" t="n">
-        <v>-10.197</v>
+          <t>영업권 상각</t>
+        </is>
       </c>
       <c r="I142" s="22" t="n">
-        <v>-20.345</v>
-      </c>
-      <c r="K142" s="22" t="n">
-        <v>-15.421</v>
+        <v>4.129</v>
       </c>
       <c r="M142" s="22" t="n">
-        <v>-34.839</v>
-      </c>
-      <c r="V142" s="22" t="n">
-        <v>-13.62</v>
+        <v>30.213</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>-20.345</v>
+        <v>4.129</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>-34.839</v>
+        <v>30.213</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>보험금 수익</t>
+          <t>렌털자산 취득</t>
         </is>
       </c>
       <c r="E143" s="22" t="n">
-        <v>-31.151</v>
+        <v>-6584.18</v>
       </c>
       <c r="G143" s="22" t="n">
-        <v>-10.114</v>
+        <v>-3489.134</v>
       </c>
       <c r="I143" s="22" t="n">
-        <v>-20.228</v>
+        <v>-9250.064</v>
       </c>
       <c r="K143" s="22" t="n">
-        <v>-5.197</v>
+        <v>-3754.107</v>
       </c>
       <c r="M143" s="22" t="n">
-        <v>-13.361</v>
+        <v>-9341.819</v>
       </c>
       <c r="V143" s="22" t="n">
-        <v>-31.151</v>
+        <v>-6584.18</v>
       </c>
       <c r="W143" s="22" t="n">
-        <v>-20.228</v>
+        <v>-9250.064</v>
       </c>
       <c r="X143" s="22" t="n">
-        <v>-13.361</v>
+        <v>-9341.819</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>렌털자산 매각 원가대체</t>
         </is>
       </c>
       <c r="E144" s="22" t="n">
-        <v>344.736</v>
+        <v>26.504</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>205.004</v>
+        <v>7.894</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>464.823</v>
+        <v>29.019</v>
       </c>
       <c r="K144" s="22" t="n">
-        <v>286.436</v>
+        <v>17.249</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>639.326</v>
+        <v>43.435</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>344.736</v>
+        <v>26.504</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>464.823</v>
+        <v>29.019</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>639.326</v>
+        <v>43.435</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>대손충당금 증감</t>
         </is>
       </c>
       <c r="E145" s="22" t="n">
-        <v>56.951</v>
+        <v>79.681</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>8.406000000000001</v>
+        <v>73.45099999999999</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>68.627</v>
+        <v>55.414</v>
       </c>
       <c r="K145" s="22" t="n">
-        <v>10.201</v>
+        <v>134.958</v>
       </c>
       <c r="M145" s="22" t="n">
-        <v>80.24299999999999</v>
+        <v>132.662</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>56.951</v>
+        <v>79.681</v>
       </c>
       <c r="W145" s="22" t="n">
-        <v>68.627</v>
+        <v>55.414</v>
       </c>
       <c r="X145" s="22" t="n">
-        <v>80.24299999999999</v>
+        <v>132.662</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>지분법손익</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="E146" s="22" t="n">
-        <v>177.55</v>
+        <v>115.373</v>
       </c>
       <c r="G146" s="22" t="n">
-        <v>97.747</v>
+        <v>66.374</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>96.678</v>
+        <v>163.19</v>
       </c>
       <c r="K146" s="22" t="n">
-        <v>44.041</v>
+        <v>37.846</v>
       </c>
       <c r="M146" s="22" t="n">
-        <v>11.133</v>
+        <v>38.587</v>
       </c>
       <c r="V146" s="22" t="n">
-        <v>177.55</v>
+        <v>115.373</v>
       </c>
       <c r="W146" s="22" t="n">
-        <v>96.678</v>
+        <v>163.19</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>11.133</v>
+        <v>38.587</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각·매각손익</t>
+          <t>퇴직급여부채 증감</t>
         </is>
       </c>
       <c r="E147" s="22" t="n">
-        <v>1.24</v>
+        <v>64.167</v>
       </c>
       <c r="G147" s="22" t="n">
-        <v>0.75</v>
+        <v>19.07</v>
       </c>
       <c r="I147" s="22" t="n">
-        <v>-7.611</v>
+        <v>54.689</v>
       </c>
       <c r="K147" s="22" t="n">
-        <v>-1.685</v>
+        <v>13.767</v>
       </c>
       <c r="M147" s="22" t="n">
-        <v>3.816</v>
+        <v>11.202</v>
       </c>
       <c r="V147" s="22" t="n">
-        <v>1.24</v>
+        <v>64.167</v>
       </c>
       <c r="W147" s="22" t="n">
-        <v>-7.611</v>
+        <v>54.689</v>
       </c>
       <c r="X147" s="22" t="n">
-        <v>3.816</v>
+        <v>11.202</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>손상차손</t>
-        </is>
+          <t>주식보상비용</t>
+        </is>
+      </c>
+      <c r="E148" s="22" t="n">
+        <v>58.768</v>
+      </c>
+      <c r="G148" s="22" t="n">
+        <v>35.372</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>0</v>
+        <v>75.566</v>
+      </c>
+      <c r="K148" s="22" t="n">
+        <v>41.948</v>
       </c>
       <c r="M148" s="22" t="n">
-        <v>26.187</v>
+        <v>88.355</v>
+      </c>
+      <c r="V148" s="22" t="n">
+        <v>58.768</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>0</v>
+        <v>75.566</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>26.187</v>
+        <v>88.355</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>단계적 취득 차손익</t>
-        </is>
+          <t>이자·배당금 수익</t>
+        </is>
+      </c>
+      <c r="E149" s="22" t="n">
+        <v>-13.62</v>
       </c>
       <c r="G149" s="22" t="n">
-        <v>0</v>
+        <v>-10.197</v>
       </c>
       <c r="I149" s="22" t="n">
-        <v>0</v>
+        <v>-20.345</v>
       </c>
       <c r="K149" s="22" t="n">
-        <v>-39.355</v>
+        <v>-15.421</v>
       </c>
       <c r="M149" s="22" t="n">
-        <v>-39.355</v>
+        <v>-34.839</v>
+      </c>
+      <c r="V149" s="22" t="n">
+        <v>-13.62</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>0</v>
+        <v>-20.345</v>
       </c>
       <c r="X149" s="22" t="n">
-        <v>-39.355</v>
+        <v>-34.839</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>보험금 수익</t>
         </is>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-604.453</v>
+        <v>-31.151</v>
       </c>
       <c r="G150" s="22" t="n">
-        <v>-1615.306</v>
+        <v>-10.114</v>
       </c>
       <c r="I150" s="22" t="n">
-        <v>-326.446</v>
+        <v>-20.228</v>
       </c>
       <c r="K150" s="22" t="n">
-        <v>-1092.193</v>
+        <v>-5.197</v>
       </c>
       <c r="M150" s="22" t="n">
-        <v>-282.557</v>
+        <v>-13.361</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>-604.453</v>
+        <v>-31.151</v>
       </c>
       <c r="W150" s="22" t="n">
-        <v>-326.446</v>
+        <v>-20.228</v>
       </c>
       <c r="X150" s="22" t="n">
-        <v>-282.557</v>
+        <v>-13.361</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="E151" s="22" t="n">
-        <v>-162.74</v>
+        <v>344.736</v>
       </c>
       <c r="G151" s="22" t="n">
-        <v>24.99</v>
+        <v>205.004</v>
       </c>
       <c r="I151" s="22" t="n">
-        <v>79.416</v>
+        <v>464.823</v>
       </c>
       <c r="K151" s="22" t="n">
-        <v>5.68</v>
+        <v>286.436</v>
       </c>
       <c r="M151" s="22" t="n">
-        <v>65.197</v>
+        <v>639.326</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>-162.74</v>
+        <v>344.736</v>
       </c>
       <c r="W151" s="22" t="n">
-        <v>79.416</v>
+        <v>464.823</v>
       </c>
       <c r="X151" s="22" t="n">
-        <v>65.197</v>
+        <v>639.326</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>지급수수료</t>
         </is>
       </c>
       <c r="E152" s="22" t="n">
-        <v>441.514</v>
+        <v>56.951</v>
       </c>
       <c r="G152" s="22" t="n">
-        <v>634.893</v>
+        <v>8.406000000000001</v>
       </c>
       <c r="I152" s="22" t="n">
-        <v>299.097</v>
+        <v>68.627</v>
       </c>
       <c r="K152" s="22" t="n">
-        <v>-9.484999999999999</v>
+        <v>10.201</v>
       </c>
       <c r="M152" s="22" t="n">
-        <v>-3195.288</v>
+        <v>80.24299999999999</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>441.514</v>
+        <v>56.951</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>299.097</v>
+        <v>68.627</v>
       </c>
       <c r="X152" s="22" t="n">
-        <v>-3195.288</v>
+        <v>80.24299999999999</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>기타 자산 증감</t>
+          <t>지분법손익</t>
         </is>
       </c>
       <c r="E153" s="22" t="n">
-        <v>-453.758</v>
+        <v>177.55</v>
       </c>
       <c r="G153" s="22" t="n">
-        <v>-50.97</v>
+        <v>97.747</v>
       </c>
       <c r="I153" s="22" t="n">
-        <v>-41.4</v>
+        <v>96.678</v>
       </c>
       <c r="K153" s="22" t="n">
-        <v>-78.32899999999999</v>
+        <v>44.041</v>
       </c>
       <c r="M153" s="22" t="n">
-        <v>187.779</v>
+        <v>11.133</v>
       </c>
       <c r="V153" s="22" t="n">
-        <v>-453.758</v>
+        <v>177.55</v>
       </c>
       <c r="W153" s="22" t="n">
-        <v>-41.4</v>
+        <v>96.678</v>
       </c>
       <c r="X153" s="22" t="n">
-        <v>187.779</v>
+        <v>11.133</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>기타 부채 증감</t>
+          <t>고정자산 제각·매각손익</t>
         </is>
       </c>
       <c r="E154" s="22" t="n">
-        <v>878.619</v>
+        <v>1.24</v>
       </c>
       <c r="G154" s="22" t="n">
-        <v>381.217</v>
+        <v>0.75</v>
       </c>
       <c r="I154" s="22" t="n">
-        <v>114.494</v>
+        <v>-7.611</v>
       </c>
       <c r="K154" s="22" t="n">
-        <v>737.84</v>
+        <v>-1.685</v>
       </c>
       <c r="M154" s="22" t="n">
-        <v>527.779</v>
+        <v>3.816</v>
       </c>
       <c r="V154" s="22" t="n">
-        <v>878.619</v>
+        <v>1.24</v>
       </c>
       <c r="W154" s="22" t="n">
-        <v>114.494</v>
+        <v>-7.611</v>
       </c>
       <c r="X154" s="22" t="n">
-        <v>527.779</v>
+        <v>3.816</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
-        </is>
-      </c>
-      <c r="E155" s="22" t="n">
-        <v>-15.494</v>
-      </c>
-      <c r="G155" s="22" t="n">
-        <v>88.751</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="I155" s="22" t="n">
-        <v>185.355</v>
-      </c>
-      <c r="K155" s="22" t="n">
-        <v>228.445</v>
+        <v>0</v>
       </c>
       <c r="M155" s="22" t="n">
-        <v>425.005</v>
-      </c>
-      <c r="V155" s="22" t="n">
-        <v>-15.494</v>
+        <v>26.187</v>
       </c>
       <c r="W155" s="22" t="n">
-        <v>185.355</v>
+        <v>0</v>
       </c>
       <c r="X155" s="22" t="n">
-        <v>425.005</v>
+        <v>26.187</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="E156" s="22" t="n">
-        <v>-216.309</v>
+          <t>단계적 취득 차손익</t>
+        </is>
       </c>
       <c r="G156" s="22" t="n">
-        <v>-20.028</v>
+        <v>0</v>
       </c>
       <c r="I156" s="22" t="n">
-        <v>143.323</v>
+        <v>0</v>
       </c>
       <c r="K156" s="22" t="n">
-        <v>23.515</v>
+        <v>-39.355</v>
       </c>
       <c r="M156" s="22" t="n">
-        <v>117.829</v>
-      </c>
-      <c r="V156" s="22" t="n">
-        <v>-216.309</v>
+        <v>-39.355</v>
       </c>
       <c r="W156" s="22" t="n">
-        <v>143.323</v>
+        <v>0</v>
       </c>
       <c r="X156" s="22" t="n">
-        <v>117.829</v>
+        <v>-39.355</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="E157" s="22" t="n">
-        <v>4425.198</v>
+        <v>-604.453</v>
       </c>
       <c r="G157" s="22" t="n">
-        <v>2633.486</v>
+        <v>-1615.306</v>
       </c>
       <c r="I157" s="22" t="n">
-        <v>3484.147</v>
+        <v>-326.446</v>
       </c>
       <c r="K157" s="22" t="n">
-        <v>3412.511</v>
+        <v>-1092.193</v>
       </c>
       <c r="M157" s="22" t="n">
-        <v>2191.619</v>
+        <v>-282.557</v>
       </c>
       <c r="V157" s="22" t="n">
-        <v>4425.198</v>
+        <v>-604.453</v>
       </c>
       <c r="W157" s="22" t="n">
-        <v>3484.147</v>
+        <v>-326.446</v>
       </c>
       <c r="X157" s="22" t="n">
-        <v>2191.619</v>
+        <v>-282.557</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="E158" s="22" t="n">
-        <v>13.62</v>
+        <v>-162.74</v>
       </c>
       <c r="G158" s="22" t="n">
-        <v>10.424</v>
+        <v>24.99</v>
       </c>
       <c r="I158" s="22" t="n">
-        <v>25.296</v>
+        <v>79.416</v>
       </c>
       <c r="K158" s="22" t="n">
-        <v>10.687</v>
+        <v>5.68</v>
       </c>
       <c r="M158" s="22" t="n">
-        <v>29.769</v>
+        <v>65.197</v>
       </c>
       <c r="V158" s="22" t="n">
-        <v>13.62</v>
+        <v>-162.74</v>
       </c>
       <c r="W158" s="22" t="n">
-        <v>25.296</v>
+        <v>79.416</v>
       </c>
       <c r="X158" s="22" t="n">
-        <v>29.769</v>
+        <v>65.197</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="E159" s="22" t="n">
-        <v>-351.725</v>
+        <v>441.514</v>
       </c>
       <c r="G159" s="22" t="n">
-        <v>-210.513</v>
+        <v>634.893</v>
       </c>
       <c r="I159" s="22" t="n">
-        <v>-462.446</v>
+        <v>299.097</v>
       </c>
       <c r="K159" s="22" t="n">
-        <v>-282.88</v>
+        <v>-9.484999999999999</v>
       </c>
       <c r="M159" s="22" t="n">
-        <v>-631.557</v>
+        <v>-3195.288</v>
       </c>
       <c r="V159" s="22" t="n">
-        <v>-351.725</v>
+        <v>441.514</v>
       </c>
       <c r="W159" s="22" t="n">
-        <v>-462.446</v>
+        <v>299.097</v>
       </c>
       <c r="X159" s="22" t="n">
-        <v>-631.557</v>
+        <v>-3195.288</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>보험금 수취</t>
+          <t>기타 자산 증감</t>
         </is>
       </c>
       <c r="E160" s="22" t="n">
-        <v>31.151</v>
+        <v>-453.758</v>
       </c>
       <c r="G160" s="22" t="n">
-        <v>10.114</v>
+        <v>-50.97</v>
       </c>
       <c r="I160" s="22" t="n">
-        <v>20.228</v>
+        <v>-41.4</v>
       </c>
       <c r="K160" s="22" t="n">
-        <v>5.197</v>
+        <v>-78.32899999999999</v>
       </c>
       <c r="M160" s="22" t="n">
-        <v>13.361</v>
+        <v>187.779</v>
       </c>
       <c r="V160" s="22" t="n">
-        <v>31.151</v>
+        <v>-453.758</v>
       </c>
       <c r="W160" s="22" t="n">
-        <v>20.228</v>
+        <v>-41.4</v>
       </c>
       <c r="X160" s="22" t="n">
-        <v>13.361</v>
+        <v>187.779</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부·환급</t>
+          <t>기타 부채 증감</t>
         </is>
       </c>
       <c r="E161" s="22" t="n">
-        <v>-915.145</v>
+        <v>878.619</v>
       </c>
       <c r="G161" s="22" t="n">
-        <v>-586.753</v>
+        <v>381.217</v>
       </c>
       <c r="I161" s="22" t="n">
-        <v>-1070.14</v>
+        <v>114.494</v>
       </c>
       <c r="K161" s="22" t="n">
-        <v>-593.491</v>
+        <v>737.84</v>
       </c>
       <c r="M161" s="22" t="n">
-        <v>-1192.639</v>
+        <v>527.779</v>
       </c>
       <c r="V161" s="22" t="n">
-        <v>-915.145</v>
+        <v>878.619</v>
       </c>
       <c r="W161" s="22" t="n">
-        <v>-1070.14</v>
+        <v>114.494</v>
       </c>
       <c r="X161" s="22" t="n">
-        <v>-1192.639</v>
+        <v>527.779</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E162" s="12" t="n">
-        <v>3203.099</v>
-      </c>
-      <c r="G162" s="12" t="n">
-        <v>1856.758</v>
-      </c>
-      <c r="I162" s="12" t="n">
-        <v>1997.084</v>
-      </c>
-      <c r="K162" s="12" t="n">
-        <v>2552.024</v>
-      </c>
-      <c r="M162" s="12" t="n">
-        <v>410.553</v>
-      </c>
-      <c r="V162" s="12" t="n">
-        <v>3203.099</v>
-      </c>
-      <c r="W162" s="12" t="n">
-        <v>1997.084</v>
-      </c>
-      <c r="X162" s="12" t="n">
-        <v>410.553</v>
+      <c r="A162" s="20" t="inlineStr">
+        <is>
+          <t>미지급 소비세 증감</t>
+        </is>
+      </c>
+      <c r="E162" s="22" t="n">
+        <v>-15.494</v>
+      </c>
+      <c r="G162" s="22" t="n">
+        <v>88.751</v>
+      </c>
+      <c r="I162" s="22" t="n">
+        <v>185.355</v>
+      </c>
+      <c r="K162" s="22" t="n">
+        <v>228.445</v>
+      </c>
+      <c r="M162" s="22" t="n">
+        <v>425.005</v>
+      </c>
+      <c r="V162" s="22" t="n">
+        <v>-15.494</v>
+      </c>
+      <c r="W162" s="22" t="n">
+        <v>185.355</v>
+      </c>
+      <c r="X162" s="22" t="n">
+        <v>425.005</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>정기예금 예입</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E163" s="22" t="n">
-        <v>-96.035</v>
+        <v>-216.309</v>
       </c>
       <c r="G163" s="22" t="n">
-        <v>-90.03700000000001</v>
+        <v>-20.028</v>
       </c>
       <c r="I163" s="22" t="n">
-        <v>-96.03700000000001</v>
+        <v>143.323</v>
       </c>
       <c r="K163" s="22" t="n">
-        <v>-89.126</v>
+        <v>23.515</v>
       </c>
       <c r="M163" s="22" t="n">
-        <v>-221.626</v>
+        <v>117.829</v>
       </c>
       <c r="V163" s="22" t="n">
-        <v>-96.035</v>
+        <v>-216.309</v>
       </c>
       <c r="W163" s="22" t="n">
-        <v>-96.03700000000001</v>
+        <v>143.323</v>
       </c>
       <c r="X163" s="22" t="n">
-        <v>-221.626</v>
+        <v>117.829</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="E164" s="22" t="n">
-        <v>84.03400000000001</v>
+        <v>4425.198</v>
       </c>
       <c r="G164" s="22" t="n">
-        <v>96.035</v>
+        <v>2633.486</v>
       </c>
       <c r="I164" s="22" t="n">
-        <v>96.035</v>
+        <v>3484.147</v>
       </c>
       <c r="K164" s="22" t="n">
-        <v>96.03700000000001</v>
+        <v>3412.511</v>
       </c>
       <c r="M164" s="22" t="n">
-        <v>96.03700000000001</v>
+        <v>2191.619</v>
       </c>
       <c r="V164" s="22" t="n">
-        <v>84.03400000000001</v>
+        <v>4425.198</v>
       </c>
       <c r="W164" s="22" t="n">
-        <v>96.035</v>
+        <v>3484.147</v>
       </c>
       <c r="X164" s="22" t="n">
-        <v>96.03700000000001</v>
+        <v>2191.619</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="E165" s="22" t="n">
-        <v>-970.763</v>
+        <v>13.62</v>
       </c>
       <c r="G165" s="22" t="n">
-        <v>-455.959</v>
+        <v>10.424</v>
       </c>
       <c r="I165" s="22" t="n">
-        <v>-1082.944</v>
+        <v>25.296</v>
       </c>
       <c r="K165" s="22" t="n">
-        <v>-457.826</v>
+        <v>10.687</v>
       </c>
       <c r="M165" s="22" t="n">
-        <v>-1702.021</v>
+        <v>29.769</v>
       </c>
       <c r="V165" s="22" t="n">
-        <v>-970.763</v>
+        <v>13.62</v>
       </c>
       <c r="W165" s="22" t="n">
-        <v>-1082.944</v>
+        <v>25.296</v>
       </c>
       <c r="X165" s="22" t="n">
-        <v>-1702.021</v>
+        <v>29.769</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="E166" s="22" t="n">
-        <v>7.583</v>
+        <v>-351.725</v>
       </c>
       <c r="G166" s="22" t="n">
-        <v>2.792</v>
+        <v>-210.513</v>
       </c>
       <c r="I166" s="22" t="n">
-        <v>15.424</v>
+        <v>-462.446</v>
       </c>
       <c r="K166" s="22" t="n">
-        <v>8.243</v>
+        <v>-282.88</v>
       </c>
       <c r="M166" s="22" t="n">
-        <v>14.545</v>
+        <v>-631.557</v>
       </c>
       <c r="V166" s="22" t="n">
-        <v>7.583</v>
+        <v>-351.725</v>
       </c>
       <c r="W166" s="22" t="n">
-        <v>15.424</v>
+        <v>-462.446</v>
       </c>
       <c r="X166" s="22" t="n">
-        <v>14.545</v>
+        <v>-631.557</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>보험금 수취</t>
         </is>
       </c>
       <c r="E167" s="22" t="n">
-        <v>-69.705</v>
+        <v>31.151</v>
       </c>
       <c r="G167" s="22" t="n">
-        <v>-48.242</v>
+        <v>10.114</v>
       </c>
       <c r="I167" s="22" t="n">
-        <v>-100.685</v>
+        <v>20.228</v>
       </c>
       <c r="K167" s="22" t="n">
-        <v>-49.593</v>
+        <v>5.197</v>
       </c>
       <c r="M167" s="22" t="n">
-        <v>-104.388</v>
+        <v>13.361</v>
       </c>
       <c r="V167" s="22" t="n">
-        <v>-69.705</v>
+        <v>31.151</v>
       </c>
       <c r="W167" s="22" t="n">
-        <v>-100.685</v>
+        <v>20.228</v>
       </c>
       <c r="X167" s="22" t="n">
-        <v>-104.388</v>
+        <v>13.361</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
-        </is>
+          <t>법인세 납부·환급</t>
+        </is>
+      </c>
+      <c r="E168" s="22" t="n">
+        <v>-915.145</v>
       </c>
       <c r="G168" s="22" t="n">
-        <v>0</v>
+        <v>-586.753</v>
       </c>
       <c r="I168" s="22" t="n">
-        <v>0</v>
+        <v>-1070.14</v>
       </c>
       <c r="K168" s="22" t="n">
-        <v>-1134.601</v>
+        <v>-593.491</v>
       </c>
       <c r="M168" s="22" t="n">
-        <v>-1134.601</v>
+        <v>-1192.639</v>
+      </c>
+      <c r="V168" s="22" t="n">
+        <v>-915.145</v>
       </c>
       <c r="W168" s="22" t="n">
-        <v>0</v>
+        <v>-1070.14</v>
       </c>
       <c r="X168" s="22" t="n">
-        <v>-1134.601</v>
+        <v>-1192.639</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="E169" s="22" t="n">
-        <v>-74.145</v>
-      </c>
-      <c r="G169" s="22" t="n">
-        <v>-147.361</v>
-      </c>
-      <c r="I169" s="22" t="n">
-        <v>-207.341</v>
-      </c>
-      <c r="K169" s="22" t="n">
-        <v>-108.497</v>
-      </c>
-      <c r="M169" s="22" t="n">
-        <v>-111.359</v>
-      </c>
-      <c r="V169" s="22" t="n">
-        <v>-74.145</v>
-      </c>
-      <c r="W169" s="22" t="n">
-        <v>-207.341</v>
-      </c>
-      <c r="X169" s="22" t="n">
-        <v>-111.359</v>
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="n">
+        <v>3203.099</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>1856.758</v>
+      </c>
+      <c r="I169" s="12" t="n">
+        <v>1997.084</v>
+      </c>
+      <c r="K169" s="12" t="n">
+        <v>2552.024</v>
+      </c>
+      <c r="M169" s="12" t="n">
+        <v>410.553</v>
+      </c>
+      <c r="V169" s="12" t="n">
+        <v>3203.099</v>
+      </c>
+      <c r="W169" s="12" t="n">
+        <v>1997.084</v>
+      </c>
+      <c r="X169" s="12" t="n">
+        <v>410.553</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E170" s="12" t="n">
-        <v>-1119.033</v>
-      </c>
-      <c r="G170" s="12" t="n">
-        <v>-642.772</v>
-      </c>
-      <c r="I170" s="12" t="n">
-        <v>-1375.547</v>
-      </c>
-      <c r="K170" s="12" t="n">
-        <v>-1735.364</v>
-      </c>
-      <c r="M170" s="12" t="n">
-        <v>-3163.414</v>
-      </c>
-      <c r="V170" s="12" t="n">
-        <v>-1119.033</v>
-      </c>
-      <c r="W170" s="12" t="n">
-        <v>-1375.547</v>
-      </c>
-      <c r="X170" s="12" t="n">
-        <v>-3163.414</v>
+      <c r="A170" s="20" t="inlineStr">
+        <is>
+          <t>정기예금 예입</t>
+        </is>
+      </c>
+      <c r="E170" s="22" t="n">
+        <v>-96.035</v>
+      </c>
+      <c r="G170" s="22" t="n">
+        <v>-90.03700000000001</v>
+      </c>
+      <c r="I170" s="22" t="n">
+        <v>-96.03700000000001</v>
+      </c>
+      <c r="K170" s="22" t="n">
+        <v>-89.126</v>
+      </c>
+      <c r="M170" s="22" t="n">
+        <v>-221.626</v>
+      </c>
+      <c r="V170" s="22" t="n">
+        <v>-96.035</v>
+      </c>
+      <c r="W170" s="22" t="n">
+        <v>-96.03700000000001</v>
+      </c>
+      <c r="X170" s="22" t="n">
+        <v>-221.626</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 순증감</t>
+          <t>정기예금 인출</t>
         </is>
       </c>
       <c r="E171" s="22" t="n">
-        <v>53.02</v>
+        <v>84.03400000000001</v>
       </c>
       <c r="G171" s="22" t="n">
-        <v>1062.48</v>
+        <v>96.035</v>
       </c>
       <c r="I171" s="22" t="n">
-        <v>-1513.38</v>
+        <v>96.035</v>
       </c>
       <c r="K171" s="22" t="n">
-        <v>1579.966</v>
+        <v>96.03700000000001</v>
       </c>
       <c r="M171" s="22" t="n">
-        <v>-1073.808</v>
+        <v>96.03700000000001</v>
       </c>
       <c r="V171" s="22" t="n">
-        <v>53.02</v>
+        <v>84.03400000000001</v>
       </c>
       <c r="W171" s="22" t="n">
-        <v>-1513.38</v>
+        <v>96.035</v>
       </c>
       <c r="X171" s="22" t="n">
-        <v>-1073.808</v>
+        <v>96.03700000000001</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="E172" s="22" t="n">
-        <v>6015.5</v>
+        <v>-970.763</v>
       </c>
       <c r="G172" s="22" t="n">
-        <v>752</v>
+        <v>-455.959</v>
       </c>
       <c r="I172" s="22" t="n">
-        <v>8461.17</v>
+        <v>-1082.944</v>
       </c>
       <c r="K172" s="22" t="n">
-        <v>290.461</v>
+        <v>-457.826</v>
       </c>
       <c r="M172" s="22" t="n">
-        <v>11320.361</v>
+        <v>-1702.021</v>
       </c>
       <c r="V172" s="22" t="n">
-        <v>6015.5</v>
+        <v>-970.763</v>
       </c>
       <c r="W172" s="22" t="n">
-        <v>8461.17</v>
+        <v>-1082.944</v>
       </c>
       <c r="X172" s="22" t="n">
-        <v>11320.361</v>
+        <v>-1702.021</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
+          <t>유형자산 매각</t>
         </is>
       </c>
       <c r="E173" s="22" t="n">
-        <v>-3893.761</v>
+        <v>7.583</v>
       </c>
       <c r="G173" s="22" t="n">
-        <v>-2186.738</v>
+        <v>2.792</v>
       </c>
       <c r="I173" s="22" t="n">
-        <v>-4477.38</v>
+        <v>15.424</v>
       </c>
       <c r="K173" s="22" t="n">
-        <v>-2712.696</v>
+        <v>8.243</v>
       </c>
       <c r="M173" s="22" t="n">
-        <v>-5498.79</v>
+        <v>14.545</v>
       </c>
       <c r="V173" s="22" t="n">
-        <v>-3893.761</v>
+        <v>7.583</v>
       </c>
       <c r="W173" s="22" t="n">
-        <v>-4477.38</v>
+        <v>15.424</v>
       </c>
       <c r="X173" s="22" t="n">
-        <v>-5498.79</v>
+        <v>14.545</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="20" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="E174" s="22" t="n">
-        <v>-2509.06</v>
+        <v>-69.705</v>
       </c>
       <c r="G174" s="22" t="n">
-        <v>-1276.73</v>
+        <v>-48.242</v>
       </c>
       <c r="I174" s="22" t="n">
-        <v>-1838.354</v>
+        <v>-100.685</v>
       </c>
       <c r="K174" s="22" t="n">
-        <v>-935.77</v>
+        <v>-49.593</v>
       </c>
       <c r="M174" s="22" t="n">
-        <v>-1812.226</v>
+        <v>-104.388</v>
       </c>
       <c r="V174" s="22" t="n">
-        <v>-2509.06</v>
+        <v>-69.705</v>
       </c>
       <c r="W174" s="22" t="n">
-        <v>-1838.354</v>
+        <v>-100.685</v>
       </c>
       <c r="X174" s="22" t="n">
-        <v>-1812.226</v>
+        <v>-104.388</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>사채 상환</t>
-        </is>
-      </c>
-      <c r="E175" s="22" t="n">
-        <v>-30</v>
+          <t>연결범위 변경 자회사 주식 취득</t>
+        </is>
       </c>
       <c r="G175" s="22" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="I175" s="22" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="K175" s="22" t="n">
-        <v>-15</v>
+        <v>-1134.601</v>
       </c>
       <c r="M175" s="22" t="n">
-        <v>-30</v>
-      </c>
-      <c r="V175" s="22" t="n">
-        <v>-30</v>
+        <v>-1134.601</v>
       </c>
       <c r="W175" s="22" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="X175" s="22" t="n">
-        <v>-30</v>
+        <v>-1134.601</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="20" t="inlineStr">
         <is>
-          <t>지급수수료 지급</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E176" s="22" t="n">
-        <v>-56.951</v>
+        <v>-74.145</v>
       </c>
       <c r="G176" s="22" t="n">
-        <v>-8.406000000000001</v>
+        <v>-147.361</v>
       </c>
       <c r="I176" s="22" t="n">
-        <v>-68.627</v>
+        <v>-207.341</v>
       </c>
       <c r="K176" s="22" t="n">
-        <v>-10.201</v>
+        <v>-108.497</v>
       </c>
       <c r="M176" s="22" t="n">
-        <v>-80.24299999999999</v>
+        <v>-111.359</v>
       </c>
       <c r="V176" s="22" t="n">
-        <v>-56.951</v>
+        <v>-74.145</v>
       </c>
       <c r="W176" s="22" t="n">
-        <v>-68.627</v>
+        <v>-207.341</v>
       </c>
       <c r="X176" s="22" t="n">
-        <v>-80.24299999999999</v>
+        <v>-111.359</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="20" t="inlineStr">
-        <is>
-          <t>연결 자회사 설립 비지배주주 납입</t>
-        </is>
-      </c>
-      <c r="E177" s="22" t="n">
-        <v>487.6</v>
-      </c>
-      <c r="I177" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V177" s="22" t="n">
-        <v>487.6</v>
-      </c>
-      <c r="W177" s="22" t="n">
-        <v>0</v>
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E177" s="12" t="n">
+        <v>-1119.033</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>-642.772</v>
+      </c>
+      <c r="I177" s="12" t="n">
+        <v>-1375.547</v>
+      </c>
+      <c r="K177" s="12" t="n">
+        <v>-1735.364</v>
+      </c>
+      <c r="M177" s="12" t="n">
+        <v>-3163.414</v>
+      </c>
+      <c r="V177" s="12" t="n">
+        <v>-1119.033</v>
+      </c>
+      <c r="W177" s="12" t="n">
+        <v>-1375.547</v>
+      </c>
+      <c r="X177" s="12" t="n">
+        <v>-3163.414</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
-        </is>
+          <t>단기차입금 순증감</t>
+        </is>
+      </c>
+      <c r="E178" s="22" t="n">
+        <v>53.02</v>
       </c>
       <c r="G178" s="22" t="n">
-        <v>0</v>
+        <v>1062.48</v>
       </c>
       <c r="I178" s="22" t="n">
-        <v>0</v>
+        <v>-1513.38</v>
       </c>
       <c r="K178" s="22" t="n">
-        <v>2496.123</v>
+        <v>1579.966</v>
       </c>
       <c r="M178" s="22" t="n">
-        <v>2496.123</v>
+        <v>-1073.808</v>
+      </c>
+      <c r="V178" s="22" t="n">
+        <v>53.02</v>
       </c>
       <c r="W178" s="22" t="n">
-        <v>0</v>
+        <v>-1513.38</v>
       </c>
       <c r="X178" s="22" t="n">
-        <v>2496.123</v>
+        <v>-1073.808</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 없는 자회사 주식 취득</t>
-        </is>
+          <t>장기차입</t>
+        </is>
+      </c>
+      <c r="E179" s="22" t="n">
+        <v>6015.5</v>
       </c>
       <c r="G179" s="22" t="n">
-        <v>0</v>
+        <v>752</v>
       </c>
       <c r="I179" s="22" t="n">
-        <v>0</v>
+        <v>8461.17</v>
       </c>
       <c r="K179" s="22" t="n">
-        <v>-162.683</v>
+        <v>290.461</v>
       </c>
       <c r="M179" s="22" t="n">
-        <v>-162.683</v>
+        <v>11320.361</v>
+      </c>
+      <c r="V179" s="22" t="n">
+        <v>6015.5</v>
       </c>
       <c r="W179" s="22" t="n">
-        <v>0</v>
+        <v>8461.17</v>
       </c>
       <c r="X179" s="22" t="n">
-        <v>-162.683</v>
+        <v>11320.361</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="20" t="inlineStr">
         <is>
-          <t>자기주식 매각</t>
+          <t>장기차입금 상환</t>
         </is>
       </c>
       <c r="E180" s="22" t="n">
-        <v>0</v>
+        <v>-3893.761</v>
+      </c>
+      <c r="G180" s="22" t="n">
+        <v>-2186.738</v>
       </c>
       <c r="I180" s="22" t="n">
-        <v>396</v>
+        <v>-4477.38</v>
+      </c>
+      <c r="K180" s="22" t="n">
+        <v>-2712.696</v>
       </c>
       <c r="M180" s="22" t="n">
-        <v>0</v>
+        <v>-5498.79</v>
       </c>
       <c r="V180" s="22" t="n">
-        <v>0</v>
+        <v>-3893.761</v>
       </c>
       <c r="W180" s="22" t="n">
-        <v>396</v>
+        <v>-4477.38</v>
       </c>
       <c r="X180" s="22" t="n">
-        <v>0</v>
+        <v>-5498.79</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
+          <t>리스부채 상환</t>
         </is>
       </c>
       <c r="E181" s="22" t="n">
-        <v>-214.267</v>
+        <v>-2509.06</v>
       </c>
       <c r="G181" s="22" t="n">
-        <v>-246.501</v>
+        <v>-1276.73</v>
       </c>
       <c r="I181" s="22" t="n">
-        <v>-246.501</v>
+        <v>-1838.354</v>
       </c>
       <c r="K181" s="22" t="n">
-        <v>-576.282</v>
+        <v>-935.77</v>
       </c>
       <c r="M181" s="22" t="n">
-        <v>-576.282</v>
+        <v>-1812.226</v>
       </c>
       <c r="V181" s="22" t="n">
-        <v>-214.267</v>
+        <v>-2509.06</v>
       </c>
       <c r="W181" s="22" t="n">
-        <v>-246.501</v>
+        <v>-1838.354</v>
       </c>
       <c r="X181" s="22" t="n">
-        <v>-576.282</v>
+        <v>-1812.226</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
+          <t>사채 상환</t>
+        </is>
+      </c>
+      <c r="E182" s="22" t="n">
+        <v>-30</v>
       </c>
       <c r="G182" s="22" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I182" s="22" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="K182" s="22" t="n">
-        <v>0.014</v>
+        <v>-15</v>
       </c>
       <c r="M182" s="22" t="n">
-        <v>0.014</v>
+        <v>-30</v>
+      </c>
+      <c r="V182" s="22" t="n">
+        <v>-30</v>
       </c>
       <c r="W182" s="22" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="X182" s="22" t="n">
-        <v>0.014</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E183" s="12" t="n">
-        <v>-147.921</v>
-      </c>
-      <c r="G183" s="12" t="n">
-        <v>-1918.896</v>
-      </c>
-      <c r="I183" s="12" t="n">
-        <v>682.926</v>
-      </c>
-      <c r="K183" s="12" t="n">
-        <v>-46.068</v>
-      </c>
-      <c r="M183" s="12" t="n">
-        <v>4582.464</v>
-      </c>
-      <c r="V183" s="12" t="n">
-        <v>-147.921</v>
-      </c>
-      <c r="W183" s="12" t="n">
-        <v>682.926</v>
-      </c>
-      <c r="X183" s="12" t="n">
-        <v>4582.464</v>
+      <c r="A183" s="20" t="inlineStr">
+        <is>
+          <t>지급수수료 지급</t>
+        </is>
+      </c>
+      <c r="E183" s="22" t="n">
+        <v>-56.951</v>
+      </c>
+      <c r="G183" s="22" t="n">
+        <v>-8.406000000000001</v>
+      </c>
+      <c r="I183" s="22" t="n">
+        <v>-68.627</v>
+      </c>
+      <c r="K183" s="22" t="n">
+        <v>-10.201</v>
+      </c>
+      <c r="M183" s="22" t="n">
+        <v>-80.24299999999999</v>
+      </c>
+      <c r="V183" s="22" t="n">
+        <v>-56.951</v>
+      </c>
+      <c r="W183" s="22" t="n">
+        <v>-68.627</v>
+      </c>
+      <c r="X183" s="22" t="n">
+        <v>-80.24299999999999</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>연결 자회사 설립 비지배주주 납입</t>
         </is>
       </c>
       <c r="E184" s="22" t="n">
-        <v>16.527</v>
-      </c>
-      <c r="G184" s="22" t="n">
-        <v>17.258</v>
+        <v>487.6</v>
       </c>
       <c r="I184" s="22" t="n">
-        <v>-4.368</v>
-      </c>
-      <c r="K184" s="22" t="n">
-        <v>20.852</v>
-      </c>
-      <c r="M184" s="22" t="n">
-        <v>35.884</v>
+        <v>0</v>
       </c>
       <c r="V184" s="22" t="n">
-        <v>16.527</v>
+        <v>487.6</v>
       </c>
       <c r="W184" s="22" t="n">
-        <v>-4.368</v>
-      </c>
-      <c r="X184" s="22" t="n">
-        <v>35.884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="20" t="inlineStr">
         <is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="G185" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" s="22" t="n">
+        <v>2496.123</v>
+      </c>
+      <c r="M185" s="22" t="n">
+        <v>2496.123</v>
+      </c>
+      <c r="W185" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X185" s="22" t="n">
+        <v>2496.123</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="20" t="inlineStr">
+        <is>
+          <t>연결범위 변경 없는 자회사 주식 취득</t>
+        </is>
+      </c>
+      <c r="G186" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" s="22" t="n">
+        <v>-162.683</v>
+      </c>
+      <c r="M186" s="22" t="n">
+        <v>-162.683</v>
+      </c>
+      <c r="W186" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X186" s="22" t="n">
+        <v>-162.683</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 매각</t>
+        </is>
+      </c>
+      <c r="E187" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="22" t="n">
+        <v>396</v>
+      </c>
+      <c r="M187" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V187" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W187" s="22" t="n">
+        <v>396</v>
+      </c>
+      <c r="X187" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="E188" s="22" t="n">
+        <v>-214.267</v>
+      </c>
+      <c r="G188" s="22" t="n">
+        <v>-246.501</v>
+      </c>
+      <c r="I188" s="22" t="n">
+        <v>-246.501</v>
+      </c>
+      <c r="K188" s="22" t="n">
+        <v>-576.282</v>
+      </c>
+      <c r="M188" s="22" t="n">
+        <v>-576.282</v>
+      </c>
+      <c r="V188" s="22" t="n">
+        <v>-214.267</v>
+      </c>
+      <c r="W188" s="22" t="n">
+        <v>-246.501</v>
+      </c>
+      <c r="X188" s="22" t="n">
+        <v>-576.282</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G189" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" s="22" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="M189" s="22" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="W189" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X189" s="22" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E190" s="12" t="n">
+        <v>-147.921</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>-1918.896</v>
+      </c>
+      <c r="I190" s="12" t="n">
+        <v>682.926</v>
+      </c>
+      <c r="K190" s="12" t="n">
+        <v>-46.068</v>
+      </c>
+      <c r="M190" s="12" t="n">
+        <v>4582.464</v>
+      </c>
+      <c r="V190" s="12" t="n">
+        <v>-147.921</v>
+      </c>
+      <c r="W190" s="12" t="n">
+        <v>682.926</v>
+      </c>
+      <c r="X190" s="12" t="n">
+        <v>4582.464</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="E191" s="22" t="n">
+        <v>16.527</v>
+      </c>
+      <c r="G191" s="22" t="n">
+        <v>17.258</v>
+      </c>
+      <c r="I191" s="22" t="n">
+        <v>-4.368</v>
+      </c>
+      <c r="K191" s="22" t="n">
+        <v>20.852</v>
+      </c>
+      <c r="M191" s="22" t="n">
+        <v>35.884</v>
+      </c>
+      <c r="V191" s="22" t="n">
+        <v>16.527</v>
+      </c>
+      <c r="W191" s="22" t="n">
+        <v>-4.368</v>
+      </c>
+      <c r="X191" s="22" t="n">
+        <v>35.884</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="E185" s="22" t="n">
+      <c r="E192" s="22" t="n">
         <v>1952.672</v>
       </c>
-      <c r="G185" s="22" t="n">
+      <c r="G192" s="22" t="n">
         <v>-687.651</v>
       </c>
-      <c r="I185" s="22" t="n">
+      <c r="I192" s="22" t="n">
         <v>1300.095</v>
       </c>
-      <c r="K185" s="22" t="n">
+      <c r="K192" s="22" t="n">
         <v>791.444</v>
       </c>
-      <c r="M185" s="22" t="n">
+      <c r="M192" s="22" t="n">
         <v>1865.488</v>
       </c>
-      <c r="V185" s="22" t="n">
+      <c r="V192" s="22" t="n">
         <v>1952.672</v>
       </c>
-      <c r="W185" s="22" t="n">
+      <c r="W192" s="22" t="n">
         <v>1300.095</v>
       </c>
-      <c r="X185" s="22" t="n">
+      <c r="X192" s="22" t="n">
         <v>1865.488</v>
       </c>
     </row>
@@ -9094,7 +9433,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -10356,7 +10695,7 @@
       <c r="J42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -10400,7 +10739,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -10444,7 +10783,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -10488,7 +10827,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -10532,7 +10871,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -10576,7 +10915,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -10620,7 +10959,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -10630,35 +10969,35 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",H28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",I28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",J28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -10680,7 +11019,7 @@
       <c r="J50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -10724,7 +11063,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -10768,7 +11107,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -10812,7 +11151,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -10856,7 +11195,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -10900,7 +11239,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -10960,7 +11299,7 @@
       <c r="J57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -11004,7 +11343,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -11014,41 +11353,41 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -11058,41 +11397,41 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -11102,41 +11441,41 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -11146,35 +11485,35 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
@@ -11196,7 +11535,7 @@
       <c r="J63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -11240,7 +11579,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -11284,7 +11623,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -11328,7 +11667,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -13437,24 +13776,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
